--- a/PLOFA-2026-2027.xlsx
+++ b/PLOFA-2026-2027.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Trevor Majani\Downloads\plofa_checkpoint6\plofa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLOFA\plofa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D0006D-AC4E-4A55-AC97-63A565D6AD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336B3A6D-BCEE-42C8-A7CC-32826E0916DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="600" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{F96AC7DF-5AC7-4206-9DC5-9ED54A22FB20}"/>
   </bookViews>
@@ -2329,469 +2329,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="117">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="171" formatCode="0&quot; Days btn Oldest and Youngest&quot;"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="0&quot; Players&quot;"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="169" formatCode="0&quot; Leaders&quot;"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3362,403 +2899,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0&quot; years&quot;"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <i/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="\(0\)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <i/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.249977111117893"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -4326,6 +3466,866 @@
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="0&quot; years&quot;"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="171" formatCode="0&quot; Days btn Oldest and Youngest&quot;"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <i/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="0&quot; Players&quot;"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="\(0\)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <i/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="169" formatCode="0&quot; Leaders&quot;"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4357,115 +4357,109 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{486541C4-A908-4A02-9006-9CB38725C039}" name="Table4" displayName="Table4" ref="A1:O308" totalsRowCount="1" headerRowDxfId="116" dataDxfId="115" totalsRowDxfId="114">
-  <autoFilter ref="A1:O307" xr:uid="{486541C4-A908-4A02-9006-9CB38725C039}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="3"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{486541C4-A908-4A02-9006-9CB38725C039}" name="Table4" displayName="Table4" ref="A1:O308" totalsRowCount="1" headerRowDxfId="65" dataDxfId="64" totalsRowDxfId="63">
+  <autoFilter ref="A1:O307" xr:uid="{486541C4-A908-4A02-9006-9CB38725C039}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{61DA74BE-95B8-4A12-BED0-1F7AF2E7F4AA}" name="Matchday" totalsRowLabel="Total" dataDxfId="113" totalsRowDxfId="112"/>
-    <tableColumn id="2" xr3:uid="{9667CD3B-79FF-4D0F-A0C4-D03A898157BD}" name="Date" totalsRowFunction="custom" dataDxfId="111" totalsRowDxfId="110">
+    <tableColumn id="1" xr3:uid="{61DA74BE-95B8-4A12-BED0-1F7AF2E7F4AA}" name="Matchday" totalsRowLabel="Total" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{9667CD3B-79FF-4D0F-A0C4-D03A898157BD}" name="Date" totalsRowFunction="custom" dataDxfId="60" totalsRowDxfId="59">
       <totalsRowFormula>MAX(Table4[Date])-MIN(Table4[Date])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B984F37D-7DCF-4B8A-B471-371A2E36A110}" name="Start Time" totalsRowFunction="average" dataDxfId="109" totalsRowDxfId="108"/>
-    <tableColumn id="13" xr3:uid="{12EA3D6C-0B47-4B26-8A56-A8C4BAF39E59}" name="HT" dataDxfId="107" totalsRowDxfId="106"/>
-    <tableColumn id="10" xr3:uid="{AC133520-21B2-4CBF-AFF6-7B5DDC4EF503}" name="FT" dataDxfId="105" totalsRowDxfId="104"/>
-    <tableColumn id="4" xr3:uid="{09338D93-CC22-4DC9-8B28-61382C235C9E}" name="Home" dataDxfId="103" totalsRowDxfId="102"/>
-    <tableColumn id="5" xr3:uid="{7178BD72-6265-45D1-9DE5-578D910AB5F3}" name="Away" dataDxfId="101" totalsRowDxfId="100"/>
-    <tableColumn id="6" xr3:uid="{F01A5997-950B-4DD5-860E-19C4DAAACF87}" name="Venue" totalsRowFunction="count" dataDxfId="99" totalsRowDxfId="98"/>
-    <tableColumn id="7" xr3:uid="{D26575B2-1DDE-40AD-B52F-6320EAF979DA}" name="Capacity" totalsRowFunction="average" dataDxfId="97" totalsRowDxfId="96"/>
-    <tableColumn id="8" xr3:uid="{90946A28-2E73-42E6-8A31-37B11E916179}" name="Attendance" totalsRowFunction="average" dataDxfId="95" totalsRowDxfId="94"/>
-    <tableColumn id="9" xr3:uid="{B3BC2C1B-5D53-4D88-90AE-A86F44725EB3}" name="PLAYED" dataDxfId="93" totalsRowDxfId="92"/>
-    <tableColumn id="11" xr3:uid="{87F34767-314D-4EF5-A209-295987C6F6FF}" name="TICKET PRICE" totalsRowFunction="average" dataDxfId="91" totalsRowDxfId="90" dataCellStyle="Currency"/>
-    <tableColumn id="12" xr3:uid="{449D5A84-CBF3-45A4-B6E3-C9BEE40C9B45}" name="MATCH REVENUE" totalsRowFunction="sum" dataDxfId="89" totalsRowDxfId="88">
+    <tableColumn id="3" xr3:uid="{B984F37D-7DCF-4B8A-B471-371A2E36A110}" name="Start Time" totalsRowFunction="average" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="13" xr3:uid="{12EA3D6C-0B47-4B26-8A56-A8C4BAF39E59}" name="HT" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="10" xr3:uid="{AC133520-21B2-4CBF-AFF6-7B5DDC4EF503}" name="FT" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{09338D93-CC22-4DC9-8B28-61382C235C9E}" name="Home" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{7178BD72-6265-45D1-9DE5-578D910AB5F3}" name="Away" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{F01A5997-950B-4DD5-860E-19C4DAAACF87}" name="Venue" totalsRowFunction="count" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{D26575B2-1DDE-40AD-B52F-6320EAF979DA}" name="Capacity" totalsRowFunction="average" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{90946A28-2E73-42E6-8A31-37B11E916179}" name="Attendance" totalsRowFunction="average" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{B3BC2C1B-5D53-4D88-90AE-A86F44725EB3}" name="PLAYED" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="11" xr3:uid="{87F34767-314D-4EF5-A209-295987C6F6FF}" name="TICKET PRICE" totalsRowFunction="average" dataDxfId="40" totalsRowDxfId="39" dataCellStyle="Currency"/>
+    <tableColumn id="12" xr3:uid="{449D5A84-CBF3-45A4-B6E3-C9BEE40C9B45}" name="MATCH REVENUE" totalsRowFunction="sum" dataDxfId="38" totalsRowDxfId="37">
       <calculatedColumnFormula>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{F12C4D29-6454-4729-80AC-8D5873BE8B58}" name="TV REVENUE" dataDxfId="87" totalsRowDxfId="86"/>
-    <tableColumn id="15" xr3:uid="{C9B29167-818A-4E98-B794-7982561252A6}" name="TOT REVENUE" dataDxfId="85" totalsRowDxfId="84"/>
+    <tableColumn id="14" xr3:uid="{F12C4D29-6454-4729-80AC-8D5873BE8B58}" name="TV REVENUE" dataDxfId="36" totalsRowDxfId="35"/>
+    <tableColumn id="15" xr3:uid="{C9B29167-818A-4E98-B794-7982561252A6}" name="TOT REVENUE" dataDxfId="34" totalsRowDxfId="33"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E62FAFBA-33DE-428A-8B2A-508FB7AF2382}" name="Table2" displayName="Table2" ref="A1:X435" totalsRowCount="1" headerRowDxfId="83" dataDxfId="82" totalsRowDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E62FAFBA-33DE-428A-8B2A-508FB7AF2382}" name="Table2" displayName="Table2" ref="A1:X435" totalsRowCount="1" headerRowDxfId="116" dataDxfId="115" totalsRowDxfId="114">
   <autoFilter ref="A1:X434" xr:uid="{E62FAFBA-33DE-428A-8B2A-508FB7AF2382}"/>
   <tableColumns count="24">
-    <tableColumn id="1" xr3:uid="{5100D2B8-23FF-4D94-A60D-19E7F66E2721}" name="CLUB" totalsRowLabel="Total" dataDxfId="80" totalsRowDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{AD19320B-D334-440A-8517-F5004417DAF5}" name="LEADERSHIP" totalsRowFunction="count" dataDxfId="79" totalsRowDxfId="22"/>
-    <tableColumn id="22" xr3:uid="{D5ABF76A-EDC3-4671-AB15-3F274AF754F1}" name="ROLE" dataDxfId="78" totalsRowDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{0A804136-5D1D-4D37-916C-F1A509428F90}" name="NO" dataDxfId="77" totalsRowDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{240F9C43-5820-4360-9D80-8615A7A629CD}" name="PLAYER NAME" totalsRowFunction="count" dataDxfId="76" totalsRowDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{3CE202B4-2E7D-40AB-981D-6B27EDFB19BC}" name="POS" dataDxfId="75" totalsRowDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{8B7F162A-5FAB-42BB-96BA-1B2B9862BEB0}" name="OTHER POS" dataDxfId="74" totalsRowDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{C04841AE-0796-47FC-9142-00B0B72FE72B}" name="DOB" totalsRowFunction="custom" dataDxfId="73" totalsRowDxfId="16">
+    <tableColumn id="1" xr3:uid="{5100D2B8-23FF-4D94-A60D-19E7F66E2721}" name="CLUB" totalsRowLabel="Total" dataDxfId="113" totalsRowDxfId="112"/>
+    <tableColumn id="2" xr3:uid="{AD19320B-D334-440A-8517-F5004417DAF5}" name="LEADERSHIP" totalsRowFunction="count" dataDxfId="111" totalsRowDxfId="110"/>
+    <tableColumn id="22" xr3:uid="{D5ABF76A-EDC3-4671-AB15-3F274AF754F1}" name="ROLE" dataDxfId="109" totalsRowDxfId="108"/>
+    <tableColumn id="3" xr3:uid="{0A804136-5D1D-4D37-916C-F1A509428F90}" name="NO" dataDxfId="107" totalsRowDxfId="106"/>
+    <tableColumn id="4" xr3:uid="{240F9C43-5820-4360-9D80-8615A7A629CD}" name="PLAYER NAME" totalsRowFunction="count" dataDxfId="105" totalsRowDxfId="104"/>
+    <tableColumn id="5" xr3:uid="{3CE202B4-2E7D-40AB-981D-6B27EDFB19BC}" name="POS" dataDxfId="103" totalsRowDxfId="102"/>
+    <tableColumn id="6" xr3:uid="{8B7F162A-5FAB-42BB-96BA-1B2B9862BEB0}" name="OTHER POS" dataDxfId="101" totalsRowDxfId="100"/>
+    <tableColumn id="7" xr3:uid="{C04841AE-0796-47FC-9142-00B0B72FE72B}" name="DOB" totalsRowFunction="custom" dataDxfId="99" totalsRowDxfId="98">
       <totalsRowFormula>MAX(Table2[DOB])-MIN(Table2[DOB])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9C79A6C6-01D9-4660-9F0A-F6FFB8CA67BB}" name="AGE" totalsRowFunction="average" dataDxfId="72" totalsRowDxfId="15">
+    <tableColumn id="8" xr3:uid="{9C79A6C6-01D9-4660-9F0A-F6FFB8CA67BB}" name="AGE" totalsRowFunction="average" dataDxfId="97" totalsRowDxfId="96">
       <calculatedColumnFormula>DATEDIF(H2,TODAY(),"Y")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{0AE0D175-D7F8-4710-AEE7-55122F740E30}" name="Signed for" totalsRowFunction="sum" dataDxfId="71" totalsRowDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{A5C8430B-03A5-45E3-A91C-39DECD9EAA64}" name="Market _x000a_Value" totalsRowFunction="sum" dataDxfId="70" totalsRowDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{FC521E6F-45B4-43A1-AA9A-87ECB7827C01}" name="Salary/_x000a_Week" totalsRowFunction="sum" dataDxfId="69" totalsRowDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{A76E75F0-046B-430C-8466-C3849A91F996}" name="Salary/_x000a_Year" totalsRowFunction="sum" dataDxfId="68" totalsRowDxfId="11">
+    <tableColumn id="9" xr3:uid="{0AE0D175-D7F8-4710-AEE7-55122F740E30}" name="Signed for" totalsRowFunction="sum" dataDxfId="95" totalsRowDxfId="94"/>
+    <tableColumn id="10" xr3:uid="{A5C8430B-03A5-45E3-A91C-39DECD9EAA64}" name="Market _x000a_Value" totalsRowFunction="sum" dataDxfId="93" totalsRowDxfId="92"/>
+    <tableColumn id="11" xr3:uid="{FC521E6F-45B4-43A1-AA9A-87ECB7827C01}" name="Salary/_x000a_Week" totalsRowFunction="sum" dataDxfId="91" totalsRowDxfId="90"/>
+    <tableColumn id="12" xr3:uid="{A76E75F0-046B-430C-8466-C3849A91F996}" name="Salary/_x000a_Year" totalsRowFunction="sum" dataDxfId="89" totalsRowDxfId="88">
       <calculatedColumnFormula>(Table2[[#This Row],[Salary/
 Week]]*52)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{069E9AAC-4EE5-4B45-AEA6-8C6FBF400635}" name="Transfer_x000a_ Date" dataDxfId="67" totalsRowDxfId="10"/>
-    <tableColumn id="14" xr3:uid="{2A5D31B8-5A58-4F28-BA02-02613963F8F9}" name="Contract End" dataDxfId="66" totalsRowDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{331A1894-EE38-4E69-A045-517137DB279F}" name="Years _x000a_At" dataDxfId="65" totalsRowDxfId="8">
+    <tableColumn id="13" xr3:uid="{069E9AAC-4EE5-4B45-AEA6-8C6FBF400635}" name="Transfer_x000a_ Date" dataDxfId="87" totalsRowDxfId="86"/>
+    <tableColumn id="14" xr3:uid="{2A5D31B8-5A58-4F28-BA02-02613963F8F9}" name="Contract End" dataDxfId="85" totalsRowDxfId="84"/>
+    <tableColumn id="15" xr3:uid="{331A1894-EE38-4E69-A045-517137DB279F}" name="Years _x000a_At" dataDxfId="83" totalsRowDxfId="82">
       <calculatedColumnFormula>DATEDIF(N2,TODAY(),"Y")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{A13E980E-1D04-451D-B01B-277D960D56A5}" name="Years _x000a_Left" dataDxfId="64" totalsRowDxfId="7">
+    <tableColumn id="16" xr3:uid="{A13E980E-1D04-451D-B01B-277D960D56A5}" name="Years _x000a_Left" dataDxfId="81" totalsRowDxfId="80">
       <calculatedColumnFormula>DATEDIF(TODAY(),O2,"y")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{DE8EB871-D31E-4E34-9C8B-DF62FBF91853}" name="Months Left" dataDxfId="63" totalsRowDxfId="6">
+    <tableColumn id="17" xr3:uid="{DE8EB871-D31E-4E34-9C8B-DF62FBF91853}" name="Months Left" dataDxfId="79" totalsRowDxfId="78">
       <calculatedColumnFormula>DATEDIF(TODAY(),O2,"m")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{A2E5331A-3424-430E-B490-1E81D9F5F711}" name="M" dataDxfId="62" totalsRowDxfId="5"/>
-    <tableColumn id="19" xr3:uid="{A899E500-A5BE-4D42-82F6-45D204172D74}" name="G" dataDxfId="61" totalsRowDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{7F192D31-0427-47FD-8E41-2D75350D4B17}" name="A" dataDxfId="60" totalsRowDxfId="3"/>
-    <tableColumn id="21" xr3:uid="{BE5DA5A7-A5BD-424B-99E8-1843AA5A4F6F}" name="PREFERRED FOOT" dataDxfId="59" totalsRowDxfId="2"/>
-    <tableColumn id="23" xr3:uid="{8C8EE5CE-5895-400F-80EB-1B4C196901BD}" name="SPECIALTY" dataDxfId="58" totalsRowDxfId="1"/>
-    <tableColumn id="24" xr3:uid="{ACB082F2-D158-45D0-8A4D-261FBB1B4AF3}" name="NATIONALITY" dataDxfId="57" totalsRowDxfId="0"/>
+    <tableColumn id="18" xr3:uid="{A2E5331A-3424-430E-B490-1E81D9F5F711}" name="M" dataDxfId="77" totalsRowDxfId="76"/>
+    <tableColumn id="19" xr3:uid="{A899E500-A5BE-4D42-82F6-45D204172D74}" name="G" dataDxfId="75" totalsRowDxfId="74"/>
+    <tableColumn id="20" xr3:uid="{7F192D31-0427-47FD-8E41-2D75350D4B17}" name="A" dataDxfId="73" totalsRowDxfId="72"/>
+    <tableColumn id="21" xr3:uid="{BE5DA5A7-A5BD-424B-99E8-1843AA5A4F6F}" name="PREFERRED FOOT" dataDxfId="71" totalsRowDxfId="70"/>
+    <tableColumn id="23" xr3:uid="{8C8EE5CE-5895-400F-80EB-1B4C196901BD}" name="SPECIALTY" dataDxfId="69" totalsRowDxfId="68"/>
+    <tableColumn id="24" xr3:uid="{ACB082F2-D158-45D0-8A4D-261FBB1B4AF3}" name="NATIONALITY" dataDxfId="67" totalsRowDxfId="66"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D88E773D-FD06-44FD-9567-D4D43D60F983}" name="Table3" displayName="Table3" ref="A1:O70" totalsRowCount="1" headerRowDxfId="56" dataDxfId="55" totalsRowDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D88E773D-FD06-44FD-9567-D4D43D60F983}" name="Table3" displayName="Table3" ref="A1:O70" totalsRowCount="1" headerRowDxfId="32" dataDxfId="31" totalsRowDxfId="30">
   <autoFilter ref="A1:O69" xr:uid="{D88E773D-FD06-44FD-9567-D4D43D60F983}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N69">
     <sortCondition ref="G2:G69"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="14" xr3:uid="{8EE32F52-D9FD-45F8-8F27-E33E2AF376D5}" name="JNO" dataDxfId="53" totalsRowDxfId="52"/>
-    <tableColumn id="1" xr3:uid="{6EDABE7A-CF53-4716-9174-465A0D45D0DF}" name="TRANSFERS" totalsRowLabel="Total" dataDxfId="51" totalsRowDxfId="50"/>
-    <tableColumn id="12" xr3:uid="{E9F5C4B0-7A77-4A85-9E50-9EBD42C1E35B}" name="Pos" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{88471D87-2859-4506-811B-E749D352CD1A}" name="FROM CLUB" dataDxfId="47" totalsRowDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{0984B046-F88E-4B7D-AA3B-95CA751E0C32}" name="TO CLUB" dataDxfId="45" totalsRowDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{3E25C8A5-7A95-4245-A4EA-D44145A6D12A}" name="FEE" totalsRowFunction="sum" dataDxfId="43" totalsRowDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{289D7CA0-41E9-475A-90EB-F73903BCE7CE}" name="Transfer Date" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{629A3603-6857-45C1-B69E-7867FDD82D0C}" name="Contract End" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{B2044E70-4874-4E11-93E0-AF24D7D0911D}" name="Wages" dataDxfId="37" totalsRowDxfId="36"/>
-    <tableColumn id="8" xr3:uid="{FE40BDC1-648F-4DD3-9785-87A4951EB16C}" name="DOB" dataDxfId="35" totalsRowDxfId="34"/>
-    <tableColumn id="9" xr3:uid="{85A4C7E6-EE3B-4B7D-BC62-E816F8566973}" name="Age" totalsRowFunction="average" dataDxfId="33" totalsRowDxfId="32">
+    <tableColumn id="14" xr3:uid="{8EE32F52-D9FD-45F8-8F27-E33E2AF376D5}" name="JNO" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{6EDABE7A-CF53-4716-9174-465A0D45D0DF}" name="TRANSFERS" totalsRowLabel="Total" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{E9F5C4B0-7A77-4A85-9E50-9EBD42C1E35B}" name="Pos" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{88471D87-2859-4506-811B-E749D352CD1A}" name="FROM CLUB" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{0984B046-F88E-4B7D-AA3B-95CA751E0C32}" name="TO CLUB" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{3E25C8A5-7A95-4245-A4EA-D44145A6D12A}" name="FEE" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{289D7CA0-41E9-475A-90EB-F73903BCE7CE}" name="Transfer Date" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{629A3603-6857-45C1-B69E-7867FDD82D0C}" name="Contract End" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{B2044E70-4874-4E11-93E0-AF24D7D0911D}" name="Wages" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{FE40BDC1-648F-4DD3-9785-87A4951EB16C}" name="DOB" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{85A4C7E6-EE3B-4B7D-BC62-E816F8566973}" name="Age" totalsRowFunction="average" dataDxfId="9" totalsRowDxfId="8">
       <calculatedColumnFormula>DATEDIF(Table3[[#This Row],[DOB]],TODAY(),"Y")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A3CD85D2-2684-4053-BA0B-1631DF28478F}" name="Age at Transfer" totalsRowFunction="average" dataDxfId="31" totalsRowDxfId="30">
+    <tableColumn id="10" xr3:uid="{A3CD85D2-2684-4053-BA0B-1631DF28478F}" name="Age at Transfer" totalsRowFunction="average" dataDxfId="7" totalsRowDxfId="6">
       <calculatedColumnFormula>DATEDIF(Table3[[#This Row],[DOB]],Table3[[#This Row],[Transfer Date]],"Y")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{6FD8025F-C233-46AB-8D6B-281CE81F90C7}" name="Age at Contract End" totalsRowFunction="average" dataDxfId="29" totalsRowDxfId="28">
+    <tableColumn id="13" xr3:uid="{6FD8025F-C233-46AB-8D6B-281CE81F90C7}" name="Age at Contract End" totalsRowFunction="average" dataDxfId="5" totalsRowDxfId="4">
       <calculatedColumnFormula>Table3[[#This Row],[Age at Transfer]]+Table3[[#This Row],[Contract]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{9F9A14A9-F925-4CDB-8E52-576890E05398}" name="Contract" totalsRowFunction="average" dataDxfId="27" totalsRowDxfId="26">
+    <tableColumn id="11" xr3:uid="{9F9A14A9-F925-4CDB-8E52-576890E05398}" name="Contract" totalsRowFunction="average" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>DATEDIF(Table3[[#This Row],[Transfer Date]],Table3[[#This Row],[Contract End]],"Y")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{61FE5CA7-88EA-4711-896C-3255ADE46A46}" name="COMPLETED" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="15" xr3:uid="{61FE5CA7-88EA-4711-896C-3255ADE46A46}" name="COMPLETED" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4873,7 +4867,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="33">
         <v>1</v>
       </c>
@@ -4917,7 +4911,7 @@
       <c r="N2" s="39"/>
       <c r="O2" s="39"/>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -4961,7 +4955,7 @@
       <c r="N3" s="39"/>
       <c r="O3" s="39"/>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -5005,7 +4999,7 @@
       <c r="N4" s="39"/>
       <c r="O4" s="39"/>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -5049,7 +5043,7 @@
       <c r="N5" s="39"/>
       <c r="O5" s="39"/>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>1</v>
       </c>
@@ -5093,7 +5087,7 @@
       <c r="N6" s="39"/>
       <c r="O6" s="39"/>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>1</v>
       </c>
@@ -5137,7 +5131,7 @@
       <c r="N7" s="39"/>
       <c r="O7" s="39"/>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>1</v>
       </c>
@@ -5181,7 +5175,7 @@
       <c r="N8" s="39"/>
       <c r="O8" s="39"/>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>1</v>
       </c>
@@ -5225,7 +5219,7 @@
       <c r="N9" s="39"/>
       <c r="O9" s="39"/>
     </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>1</v>
       </c>
@@ -5269,7 +5263,7 @@
       <c r="N10" s="39"/>
       <c r="O10" s="39"/>
     </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>2</v>
       </c>
@@ -5313,7 +5307,7 @@
       <c r="N11" s="39"/>
       <c r="O11" s="39"/>
     </row>
-    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>2</v>
       </c>
@@ -5357,7 +5351,7 @@
       <c r="N12" s="39"/>
       <c r="O12" s="39"/>
     </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>2</v>
       </c>
@@ -5401,7 +5395,7 @@
       <c r="N13" s="39"/>
       <c r="O13" s="39"/>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>2</v>
       </c>
@@ -5445,7 +5439,7 @@
       <c r="N14" s="39"/>
       <c r="O14" s="39"/>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>2</v>
       </c>
@@ -5489,7 +5483,7 @@
       <c r="N15" s="39"/>
       <c r="O15" s="39"/>
     </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>2</v>
       </c>
@@ -5533,7 +5527,7 @@
       <c r="N16" s="39"/>
       <c r="O16" s="39"/>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>2</v>
       </c>
@@ -5577,7 +5571,7 @@
       <c r="N17" s="39"/>
       <c r="O17" s="39"/>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>2</v>
       </c>
@@ -5621,7 +5615,7 @@
       <c r="N18" s="39"/>
       <c r="O18" s="39"/>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>2</v>
       </c>
@@ -5675,8 +5669,12 @@
       <c r="C20" s="17">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="D20" s="17">
+        <v>0.5625</v>
+      </c>
+      <c r="E20" s="17">
+        <v>0.60416666666666696</v>
+      </c>
       <c r="F20" s="1" t="s">
         <v>556</v>
       </c>
@@ -5715,8 +5713,12 @@
       <c r="C21" s="17">
         <v>0.625</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="D21" s="17">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E21" s="17">
+        <v>0.70833333333333304</v>
+      </c>
       <c r="F21" s="1" t="s">
         <v>41</v>
       </c>
@@ -5755,8 +5757,12 @@
       <c r="C22" s="17">
         <v>0.625</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="D22" s="17">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E22" s="17">
+        <v>0.70833333333333304</v>
+      </c>
       <c r="F22" s="1" t="s">
         <v>305</v>
       </c>
@@ -5795,8 +5801,12 @@
       <c r="C23" s="17">
         <v>0.625</v>
       </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="D23" s="17">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E23" s="17">
+        <v>0.70833333333333304</v>
+      </c>
       <c r="F23" s="1" t="s">
         <v>236</v>
       </c>
@@ -5835,8 +5845,12 @@
       <c r="C24" s="17">
         <v>0.625</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="D24" s="17">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E24" s="17">
+        <v>0.70833333333333304</v>
+      </c>
       <c r="F24" s="1" t="s">
         <v>327</v>
       </c>
@@ -5875,8 +5889,12 @@
       <c r="C25" s="17">
         <v>0.72916666666666663</v>
       </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="D25" s="17">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E25" s="17">
+        <v>0.8125</v>
+      </c>
       <c r="F25" s="1" t="s">
         <v>186</v>
       </c>
@@ -5915,8 +5933,12 @@
       <c r="C26" s="17">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
+      <c r="D26" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="E26" s="17">
+        <v>0.66666666666666696</v>
+      </c>
       <c r="F26" s="1" t="s">
         <v>566</v>
       </c>
@@ -5955,8 +5977,12 @@
       <c r="C27" s="17">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="D27" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="E27" s="17">
+        <v>0.66666666666666696</v>
+      </c>
       <c r="F27" s="1" t="s">
         <v>139</v>
       </c>
@@ -5995,8 +6021,12 @@
       <c r="C28" s="17">
         <v>0.6875</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
+      <c r="D28" s="17">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="E28" s="17">
+        <v>0.77083333333333304</v>
+      </c>
       <c r="F28" s="1" t="s">
         <v>114</v>
       </c>
@@ -6025,7 +6055,7 @@
       <c r="N28" s="39"/>
       <c r="O28" s="39"/>
     </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>4</v>
       </c>
@@ -6035,8 +6065,12 @@
       <c r="C29" s="17">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="D29" s="17">
+        <v>0.5625</v>
+      </c>
+      <c r="E29" s="17">
+        <v>0.60416666666666696</v>
+      </c>
       <c r="F29" s="1" t="s">
         <v>163</v>
       </c>
@@ -6049,19 +6083,23 @@
       <c r="I29" s="5">
         <v>100000</v>
       </c>
-      <c r="J29" s="5"/>
+      <c r="J29" s="5">
+        <v>96908</v>
+      </c>
       <c r="K29" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L29" s="35">
+        <v>55.84</v>
+      </c>
       <c r="M29" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>5411342.7200000007</v>
       </c>
       <c r="N29" s="39"/>
       <c r="O29" s="39"/>
     </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>4</v>
       </c>
@@ -6071,8 +6109,12 @@
       <c r="C30" s="17">
         <v>0.625</v>
       </c>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
+      <c r="D30" s="17">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E30" s="17">
+        <v>0.70833333333333304</v>
+      </c>
       <c r="F30" s="1" t="s">
         <v>350</v>
       </c>
@@ -6085,19 +6127,23 @@
       <c r="I30" s="5">
         <v>23000</v>
       </c>
-      <c r="J30" s="5"/>
+      <c r="J30" s="5">
+        <v>17830</v>
+      </c>
       <c r="K30" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L30" s="35">
+        <v>44.25</v>
+      </c>
       <c r="M30" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>788977.5</v>
       </c>
       <c r="N30" s="39"/>
       <c r="O30" s="39"/>
     </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>4</v>
       </c>
@@ -6107,8 +6153,12 @@
       <c r="C31" s="17">
         <v>0.625</v>
       </c>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="D31" s="17">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E31" s="17">
+        <v>0.70833333333333304</v>
+      </c>
       <c r="F31" s="1" t="s">
         <v>371</v>
       </c>
@@ -6121,19 +6171,23 @@
       <c r="I31" s="5">
         <v>36000</v>
       </c>
-      <c r="J31" s="5"/>
+      <c r="J31" s="5">
+        <v>28552</v>
+      </c>
       <c r="K31" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L31" s="35">
+        <v>30.76</v>
+      </c>
       <c r="M31" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>878259.52</v>
       </c>
       <c r="N31" s="39"/>
       <c r="O31" s="39"/>
     </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>4</v>
       </c>
@@ -6143,8 +6197,12 @@
       <c r="C32" s="17">
         <v>0.625</v>
       </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
+      <c r="D32" s="17">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E32" s="17">
+        <v>0.70833333333333304</v>
+      </c>
       <c r="F32" s="1" t="s">
         <v>556</v>
       </c>
@@ -6157,19 +6215,23 @@
       <c r="I32" s="5">
         <v>29700</v>
       </c>
-      <c r="J32" s="5"/>
+      <c r="J32" s="5">
+        <v>25559</v>
+      </c>
       <c r="K32" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L32" s="35">
+        <v>41.42</v>
+      </c>
       <c r="M32" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>1058653.78</v>
       </c>
       <c r="N32" s="39"/>
       <c r="O32" s="39"/>
     </row>
-    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>4</v>
       </c>
@@ -6179,8 +6241,12 @@
       <c r="C33" s="17">
         <v>0.625</v>
       </c>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
+      <c r="D33" s="17">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E33" s="17">
+        <v>0.70833333333333304</v>
+      </c>
       <c r="F33" s="1" t="s">
         <v>139</v>
       </c>
@@ -6193,19 +6259,23 @@
       <c r="I33" s="5">
         <v>65000</v>
       </c>
-      <c r="J33" s="5"/>
+      <c r="J33" s="5">
+        <v>64025</v>
+      </c>
       <c r="K33" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L33" s="35">
+        <v>59.96</v>
+      </c>
       <c r="M33" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>3838939</v>
       </c>
       <c r="N33" s="39"/>
       <c r="O33" s="39"/>
     </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>4</v>
       </c>
@@ -6215,8 +6285,12 @@
       <c r="C34" s="17">
         <v>0.72916666666666663</v>
       </c>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
+      <c r="D34" s="17">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E34" s="17">
+        <v>0.8125</v>
+      </c>
       <c r="F34" s="1" t="s">
         <v>327</v>
       </c>
@@ -6229,19 +6303,23 @@
       <c r="I34" s="5">
         <v>40000</v>
       </c>
-      <c r="J34" s="5"/>
+      <c r="J34" s="5">
+        <v>33407</v>
+      </c>
       <c r="K34" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L34" s="35">
+        <v>49.49</v>
+      </c>
       <c r="M34" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>1653312.4300000002</v>
       </c>
       <c r="N34" s="39"/>
       <c r="O34" s="39"/>
     </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>4</v>
       </c>
@@ -6251,8 +6329,12 @@
       <c r="C35" s="17">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
+      <c r="D35" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="E35" s="17">
+        <v>0.66666666666666696</v>
+      </c>
       <c r="F35" s="1" t="s">
         <v>210</v>
       </c>
@@ -6265,19 +6347,23 @@
       <c r="I35" s="5">
         <v>70000</v>
       </c>
-      <c r="J35" s="5"/>
+      <c r="J35" s="5">
+        <v>41214</v>
+      </c>
       <c r="K35" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L35" s="35">
+        <v>28.51</v>
+      </c>
       <c r="M35" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>1175011.1400000001</v>
       </c>
       <c r="N35" s="39"/>
       <c r="O35" s="39"/>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>4</v>
       </c>
@@ -6287,8 +6373,12 @@
       <c r="C36" s="17">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
+      <c r="D36" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="E36" s="17">
+        <v>0.66666666666666696</v>
+      </c>
       <c r="F36" s="1" t="s">
         <v>283</v>
       </c>
@@ -6301,19 +6391,23 @@
       <c r="I36" s="5">
         <v>55000</v>
       </c>
-      <c r="J36" s="5"/>
+      <c r="J36" s="5">
+        <v>48317</v>
+      </c>
       <c r="K36" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L36" s="35">
+        <v>46.98</v>
+      </c>
       <c r="M36" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>2269932.6599999997</v>
       </c>
       <c r="N36" s="39"/>
       <c r="O36" s="39"/>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>4</v>
       </c>
@@ -6323,8 +6417,12 @@
       <c r="C37" s="17">
         <v>0.6875</v>
       </c>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
+      <c r="D37" s="17">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="E37" s="17">
+        <v>0.77083333333333404</v>
+      </c>
       <c r="F37" s="1" t="s">
         <v>91</v>
       </c>
@@ -6337,19 +6435,23 @@
       <c r="I37" s="5">
         <v>87000</v>
       </c>
-      <c r="J37" s="5"/>
+      <c r="J37" s="5">
+        <v>85695</v>
+      </c>
       <c r="K37" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L37" s="35">
+        <v>60.26</v>
+      </c>
       <c r="M37" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>5163980.7</v>
       </c>
       <c r="N37" s="39"/>
       <c r="O37" s="39"/>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>5</v>
       </c>
@@ -6359,8 +6461,12 @@
       <c r="C38" s="17">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
+      <c r="D38" s="17">
+        <v>0.5625</v>
+      </c>
+      <c r="E38" s="17">
+        <v>0.60416666666666696</v>
+      </c>
       <c r="F38" s="1" t="s">
         <v>186</v>
       </c>
@@ -6373,19 +6479,23 @@
       <c r="I38" s="5">
         <v>80000</v>
       </c>
-      <c r="J38" s="5"/>
+      <c r="J38" s="5">
+        <v>63575</v>
+      </c>
       <c r="K38" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L38" s="35">
+        <v>46.53</v>
+      </c>
       <c r="M38" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>2958144.75</v>
       </c>
       <c r="N38" s="39"/>
       <c r="O38" s="39"/>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>5</v>
       </c>
@@ -6395,8 +6505,12 @@
       <c r="C39" s="17">
         <v>0.625</v>
       </c>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
+      <c r="D39" s="17">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E39" s="17">
+        <v>0.70833333333333304</v>
+      </c>
       <c r="F39" s="1" t="s">
         <v>305</v>
       </c>
@@ -6409,19 +6523,23 @@
       <c r="I39" s="5">
         <v>45000</v>
       </c>
-      <c r="J39" s="5"/>
+      <c r="J39" s="5">
+        <v>38068</v>
+      </c>
       <c r="K39" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L39" s="35">
+        <v>40.75</v>
+      </c>
       <c r="M39" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>1551271</v>
       </c>
       <c r="N39" s="39"/>
       <c r="O39" s="39"/>
     </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>5</v>
       </c>
@@ -6431,8 +6549,12 @@
       <c r="C40" s="17">
         <v>0.625</v>
       </c>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
+      <c r="D40" s="17">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E40" s="17">
+        <v>0.70833333333333304</v>
+      </c>
       <c r="F40" s="1" t="s">
         <v>236</v>
       </c>
@@ -6445,19 +6567,23 @@
       <c r="I40" s="5">
         <v>35000</v>
       </c>
-      <c r="J40" s="5"/>
+      <c r="J40" s="5">
+        <v>21460</v>
+      </c>
       <c r="K40" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L40" s="35">
+        <v>28.97</v>
+      </c>
       <c r="M40" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>621696.19999999995</v>
       </c>
       <c r="N40" s="39"/>
       <c r="O40" s="39"/>
     </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>5</v>
       </c>
@@ -6467,8 +6593,12 @@
       <c r="C41" s="17">
         <v>0.625</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
+      <c r="D41" s="17">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E41" s="17">
+        <v>0.70833333333333304</v>
+      </c>
       <c r="F41" s="1" t="s">
         <v>371</v>
       </c>
@@ -6481,19 +6611,23 @@
       <c r="I41" s="5">
         <v>36000</v>
       </c>
-      <c r="J41" s="5"/>
+      <c r="J41" s="5">
+        <v>34909</v>
+      </c>
       <c r="K41" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L41" s="35">
+        <v>45.54</v>
+      </c>
       <c r="M41" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>1589755.8599999999</v>
       </c>
       <c r="N41" s="39"/>
       <c r="O41" s="39"/>
     </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>5</v>
       </c>
@@ -6503,8 +6637,12 @@
       <c r="C42" s="17">
         <v>0.625</v>
       </c>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
+      <c r="D42" s="17">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E42" s="17">
+        <v>0.70833333333333304</v>
+      </c>
       <c r="F42" s="1" t="s">
         <v>566</v>
       </c>
@@ -6517,19 +6655,23 @@
       <c r="I42" s="5">
         <v>8000</v>
       </c>
-      <c r="J42" s="5"/>
+      <c r="J42" s="5">
+        <v>6583</v>
+      </c>
       <c r="K42" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L42" s="35">
+        <v>43.77</v>
+      </c>
       <c r="M42" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>288137.91000000003</v>
       </c>
       <c r="N42" s="39"/>
       <c r="O42" s="39"/>
     </row>
-    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>5</v>
       </c>
@@ -6539,8 +6681,12 @@
       <c r="C43" s="17">
         <v>0.72916666666666663</v>
       </c>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
+      <c r="D43" s="17">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E43" s="17">
+        <v>0.8125</v>
+      </c>
       <c r="F43" s="1" t="s">
         <v>210</v>
       </c>
@@ -6553,19 +6699,23 @@
       <c r="I43" s="5">
         <v>70000</v>
       </c>
-      <c r="J43" s="5"/>
+      <c r="J43" s="5">
+        <v>47608</v>
+      </c>
       <c r="K43" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L43" s="35">
+        <v>30.57</v>
+      </c>
       <c r="M43" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>1455376.56</v>
       </c>
       <c r="N43" s="39"/>
       <c r="O43" s="39"/>
     </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>5</v>
       </c>
@@ -6575,8 +6725,12 @@
       <c r="C44" s="17">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
+      <c r="D44" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="E44" s="17">
+        <v>0.66666666666666696</v>
+      </c>
       <c r="F44" s="1" t="s">
         <v>557</v>
       </c>
@@ -6589,19 +6743,23 @@
       <c r="I44" s="5">
         <v>17000</v>
       </c>
-      <c r="J44" s="5"/>
+      <c r="J44" s="5">
+        <v>13275</v>
+      </c>
       <c r="K44" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L44" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L44" s="35">
+        <v>25.32</v>
+      </c>
       <c r="M44" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>336123</v>
       </c>
       <c r="N44" s="39"/>
       <c r="O44" s="39"/>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>5</v>
       </c>
@@ -6611,8 +6769,12 @@
       <c r="C45" s="17">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
+      <c r="D45" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="E45" s="17">
+        <v>0.66666666666666696</v>
+      </c>
       <c r="F45" s="1" t="s">
         <v>260</v>
       </c>
@@ -6625,19 +6787,23 @@
       <c r="I45" s="5">
         <v>40000</v>
       </c>
-      <c r="J45" s="5"/>
+      <c r="J45" s="5">
+        <v>37449</v>
+      </c>
       <c r="K45" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L45" s="35">
+        <v>41.81</v>
+      </c>
       <c r="M45" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>1565742.6900000002</v>
       </c>
       <c r="N45" s="39"/>
       <c r="O45" s="39"/>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>5</v>
       </c>
@@ -6647,8 +6813,12 @@
       <c r="C46" s="17">
         <v>0.6875</v>
       </c>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
+      <c r="D46" s="17">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="E46" s="17">
+        <v>0.77083333333333304</v>
+      </c>
       <c r="F46" s="1" t="s">
         <v>66</v>
       </c>
@@ -6661,19 +6831,23 @@
       <c r="I46" s="5">
         <v>87000</v>
       </c>
-      <c r="J46" s="5"/>
+      <c r="J46" s="5">
+        <v>85695</v>
+      </c>
       <c r="K46" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L46" s="35"/>
+        <v>1</v>
+      </c>
+      <c r="L46" s="35">
+        <v>53.58</v>
+      </c>
       <c r="M46" s="36">
         <f>Table4[[#This Row],[Attendance]]*Table4[[#This Row],[TICKET PRICE]]</f>
-        <v>0</v>
+        <v>4591538.0999999996</v>
       </c>
       <c r="N46" s="39"/>
       <c r="O46" s="39"/>
     </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>6</v>
       </c>
@@ -6709,7 +6883,7 @@
       <c r="N47" s="39"/>
       <c r="O47" s="39"/>
     </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>6</v>
       </c>
@@ -6745,7 +6919,7 @@
       <c r="N48" s="39"/>
       <c r="O48" s="39"/>
     </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>6</v>
       </c>
@@ -6781,7 +6955,7 @@
       <c r="N49" s="39"/>
       <c r="O49" s="39"/>
     </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>6</v>
       </c>
@@ -6817,7 +6991,7 @@
       <c r="N50" s="39"/>
       <c r="O50" s="39"/>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>6</v>
       </c>
@@ -6853,7 +7027,7 @@
       <c r="N51" s="39"/>
       <c r="O51" s="39"/>
     </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>6</v>
       </c>
@@ -6889,7 +7063,7 @@
       <c r="N52" s="39"/>
       <c r="O52" s="39"/>
     </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>6</v>
       </c>
@@ -6925,7 +7099,7 @@
       <c r="N53" s="39"/>
       <c r="O53" s="39"/>
     </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>6</v>
       </c>
@@ -6961,7 +7135,7 @@
       <c r="N54" s="39"/>
       <c r="O54" s="39"/>
     </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>6</v>
       </c>
@@ -6997,7 +7171,7 @@
       <c r="N55" s="39"/>
       <c r="O55" s="39"/>
     </row>
-    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>7</v>
       </c>
@@ -7033,7 +7207,7 @@
       <c r="N56" s="39"/>
       <c r="O56" s="39"/>
     </row>
-    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>7</v>
       </c>
@@ -7069,7 +7243,7 @@
       <c r="N57" s="39"/>
       <c r="O57" s="39"/>
     </row>
-    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>7</v>
       </c>
@@ -7105,7 +7279,7 @@
       <c r="N58" s="39"/>
       <c r="O58" s="39"/>
     </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>7</v>
       </c>
@@ -7141,7 +7315,7 @@
       <c r="N59" s="39"/>
       <c r="O59" s="39"/>
     </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>7</v>
       </c>
@@ -7177,7 +7351,7 @@
       <c r="N60" s="39"/>
       <c r="O60" s="39"/>
     </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>7</v>
       </c>
@@ -7213,7 +7387,7 @@
       <c r="N61" s="39"/>
       <c r="O61" s="39"/>
     </row>
-    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>7</v>
       </c>
@@ -7249,7 +7423,7 @@
       <c r="N62" s="39"/>
       <c r="O62" s="39"/>
     </row>
-    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>7</v>
       </c>
@@ -7285,7 +7459,7 @@
       <c r="N63" s="39"/>
       <c r="O63" s="39"/>
     </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>7</v>
       </c>
@@ -7321,7 +7495,7 @@
       <c r="N64" s="39"/>
       <c r="O64" s="39"/>
     </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>8</v>
       </c>
@@ -7357,7 +7531,7 @@
       <c r="N65" s="39"/>
       <c r="O65" s="39"/>
     </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>8</v>
       </c>
@@ -7393,7 +7567,7 @@
       <c r="N66" s="39"/>
       <c r="O66" s="39"/>
     </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>8</v>
       </c>
@@ -7429,7 +7603,7 @@
       <c r="N67" s="39"/>
       <c r="O67" s="39"/>
     </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>8</v>
       </c>
@@ -7465,7 +7639,7 @@
       <c r="N68" s="39"/>
       <c r="O68" s="39"/>
     </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>8</v>
       </c>
@@ -7501,7 +7675,7 @@
       <c r="N69" s="39"/>
       <c r="O69" s="39"/>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>8</v>
       </c>
@@ -7537,7 +7711,7 @@
       <c r="N70" s="39"/>
       <c r="O70" s="39"/>
     </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>8</v>
       </c>
@@ -7573,7 +7747,7 @@
       <c r="N71" s="39"/>
       <c r="O71" s="39"/>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>8</v>
       </c>
@@ -7609,7 +7783,7 @@
       <c r="N72" s="39"/>
       <c r="O72" s="39"/>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>8</v>
       </c>
@@ -7645,7 +7819,7 @@
       <c r="N73" s="39"/>
       <c r="O73" s="39"/>
     </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>9</v>
       </c>
@@ -7681,7 +7855,7 @@
       <c r="N74" s="39"/>
       <c r="O74" s="39"/>
     </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>9</v>
       </c>
@@ -7717,7 +7891,7 @@
       <c r="N75" s="39"/>
       <c r="O75" s="39"/>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>9</v>
       </c>
@@ -7753,7 +7927,7 @@
       <c r="N76" s="39"/>
       <c r="O76" s="39"/>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>9</v>
       </c>
@@ -7789,7 +7963,7 @@
       <c r="N77" s="39"/>
       <c r="O77" s="39"/>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>9</v>
       </c>
@@ -7825,7 +7999,7 @@
       <c r="N78" s="39"/>
       <c r="O78" s="39"/>
     </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>9</v>
       </c>
@@ -7861,7 +8035,7 @@
       <c r="N79" s="39"/>
       <c r="O79" s="39"/>
     </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>9</v>
       </c>
@@ -7897,7 +8071,7 @@
       <c r="N80" s="39"/>
       <c r="O80" s="39"/>
     </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>9</v>
       </c>
@@ -7933,7 +8107,7 @@
       <c r="N81" s="39"/>
       <c r="O81" s="39"/>
     </row>
-    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>9</v>
       </c>
@@ -7969,7 +8143,7 @@
       <c r="N82" s="39"/>
       <c r="O82" s="39"/>
     </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>10</v>
       </c>
@@ -8005,7 +8179,7 @@
       <c r="N83" s="39"/>
       <c r="O83" s="39"/>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>10</v>
       </c>
@@ -8041,7 +8215,7 @@
       <c r="N84" s="39"/>
       <c r="O84" s="39"/>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>10</v>
       </c>
@@ -8077,7 +8251,7 @@
       <c r="N85" s="39"/>
       <c r="O85" s="39"/>
     </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>10</v>
       </c>
@@ -8113,7 +8287,7 @@
       <c r="N86" s="39"/>
       <c r="O86" s="39"/>
     </row>
-    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>10</v>
       </c>
@@ -8149,7 +8323,7 @@
       <c r="N87" s="39"/>
       <c r="O87" s="39"/>
     </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>10</v>
       </c>
@@ -8185,7 +8359,7 @@
       <c r="N88" s="39"/>
       <c r="O88" s="39"/>
     </row>
-    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>10</v>
       </c>
@@ -8221,7 +8395,7 @@
       <c r="N89" s="39"/>
       <c r="O89" s="39"/>
     </row>
-    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>10</v>
       </c>
@@ -8257,7 +8431,7 @@
       <c r="N90" s="39"/>
       <c r="O90" s="39"/>
     </row>
-    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>10</v>
       </c>
@@ -8293,7 +8467,7 @@
       <c r="N91" s="39"/>
       <c r="O91" s="39"/>
     </row>
-    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>11</v>
       </c>
@@ -8329,7 +8503,7 @@
       <c r="N92" s="39"/>
       <c r="O92" s="39"/>
     </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>11</v>
       </c>
@@ -8365,7 +8539,7 @@
       <c r="N93" s="39"/>
       <c r="O93" s="39"/>
     </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>11</v>
       </c>
@@ -8401,7 +8575,7 @@
       <c r="N94" s="39"/>
       <c r="O94" s="39"/>
     </row>
-    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>11</v>
       </c>
@@ -8437,7 +8611,7 @@
       <c r="N95" s="39"/>
       <c r="O95" s="39"/>
     </row>
-    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>11</v>
       </c>
@@ -8473,7 +8647,7 @@
       <c r="N96" s="39"/>
       <c r="O96" s="39"/>
     </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>11</v>
       </c>
@@ -8509,7 +8683,7 @@
       <c r="N97" s="39"/>
       <c r="O97" s="39"/>
     </row>
-    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>11</v>
       </c>
@@ -8545,7 +8719,7 @@
       <c r="N98" s="39"/>
       <c r="O98" s="39"/>
     </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>11</v>
       </c>
@@ -8581,7 +8755,7 @@
       <c r="N99" s="39"/>
       <c r="O99" s="39"/>
     </row>
-    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>11</v>
       </c>
@@ -8617,7 +8791,7 @@
       <c r="N100" s="39"/>
       <c r="O100" s="39"/>
     </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>12</v>
       </c>
@@ -8653,7 +8827,7 @@
       <c r="N101" s="39"/>
       <c r="O101" s="39"/>
     </row>
-    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>12</v>
       </c>
@@ -8689,7 +8863,7 @@
       <c r="N102" s="39"/>
       <c r="O102" s="39"/>
     </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>12</v>
       </c>
@@ -8725,7 +8899,7 @@
       <c r="N103" s="39"/>
       <c r="O103" s="39"/>
     </row>
-    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>12</v>
       </c>
@@ -8761,7 +8935,7 @@
       <c r="N104" s="39"/>
       <c r="O104" s="39"/>
     </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>12</v>
       </c>
@@ -8797,7 +8971,7 @@
       <c r="N105" s="39"/>
       <c r="O105" s="39"/>
     </row>
-    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>12</v>
       </c>
@@ -8833,7 +9007,7 @@
       <c r="N106" s="39"/>
       <c r="O106" s="39"/>
     </row>
-    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>12</v>
       </c>
@@ -8869,7 +9043,7 @@
       <c r="N107" s="39"/>
       <c r="O107" s="39"/>
     </row>
-    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
         <v>12</v>
       </c>
@@ -8905,7 +9079,7 @@
       <c r="N108" s="39"/>
       <c r="O108" s="39"/>
     </row>
-    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>12</v>
       </c>
@@ -8941,7 +9115,7 @@
       <c r="N109" s="39"/>
       <c r="O109" s="39"/>
     </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>13</v>
       </c>
@@ -8977,7 +9151,7 @@
       <c r="N110" s="39"/>
       <c r="O110" s="39"/>
     </row>
-    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>13</v>
       </c>
@@ -9013,7 +9187,7 @@
       <c r="N111" s="39"/>
       <c r="O111" s="39"/>
     </row>
-    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>13</v>
       </c>
@@ -9049,7 +9223,7 @@
       <c r="N112" s="39"/>
       <c r="O112" s="39"/>
     </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>13</v>
       </c>
@@ -9085,7 +9259,7 @@
       <c r="N113" s="39"/>
       <c r="O113" s="39"/>
     </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
         <v>13</v>
       </c>
@@ -9121,7 +9295,7 @@
       <c r="N114" s="39"/>
       <c r="O114" s="39"/>
     </row>
-    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>13</v>
       </c>
@@ -9157,7 +9331,7 @@
       <c r="N115" s="39"/>
       <c r="O115" s="39"/>
     </row>
-    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
         <v>13</v>
       </c>
@@ -9193,7 +9367,7 @@
       <c r="N116" s="39"/>
       <c r="O116" s="39"/>
     </row>
-    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>13</v>
       </c>
@@ -9229,7 +9403,7 @@
       <c r="N117" s="39"/>
       <c r="O117" s="39"/>
     </row>
-    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
         <v>13</v>
       </c>
@@ -9265,7 +9439,7 @@
       <c r="N118" s="39"/>
       <c r="O118" s="39"/>
     </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>14</v>
       </c>
@@ -9301,7 +9475,7 @@
       <c r="N119" s="39"/>
       <c r="O119" s="39"/>
     </row>
-    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
         <v>14</v>
       </c>
@@ -9337,7 +9511,7 @@
       <c r="N120" s="39"/>
       <c r="O120" s="39"/>
     </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>14</v>
       </c>
@@ -9373,7 +9547,7 @@
       <c r="N121" s="39"/>
       <c r="O121" s="39"/>
     </row>
-    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>14</v>
       </c>
@@ -9409,7 +9583,7 @@
       <c r="N122" s="39"/>
       <c r="O122" s="39"/>
     </row>
-    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>14</v>
       </c>
@@ -9445,7 +9619,7 @@
       <c r="N123" s="39"/>
       <c r="O123" s="39"/>
     </row>
-    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
         <v>14</v>
       </c>
@@ -9481,7 +9655,7 @@
       <c r="N124" s="39"/>
       <c r="O124" s="39"/>
     </row>
-    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>14</v>
       </c>
@@ -9517,7 +9691,7 @@
       <c r="N125" s="39"/>
       <c r="O125" s="39"/>
     </row>
-    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
         <v>14</v>
       </c>
@@ -9553,7 +9727,7 @@
       <c r="N126" s="39"/>
       <c r="O126" s="39"/>
     </row>
-    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>14</v>
       </c>
@@ -9589,7 +9763,7 @@
       <c r="N127" s="39"/>
       <c r="O127" s="39"/>
     </row>
-    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
         <v>15</v>
       </c>
@@ -9625,7 +9799,7 @@
       <c r="N128" s="39"/>
       <c r="O128" s="39"/>
     </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>15</v>
       </c>
@@ -9661,7 +9835,7 @@
       <c r="N129" s="39"/>
       <c r="O129" s="39"/>
     </row>
-    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
         <v>15</v>
       </c>
@@ -9697,7 +9871,7 @@
       <c r="N130" s="39"/>
       <c r="O130" s="39"/>
     </row>
-    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>15</v>
       </c>
@@ -9733,7 +9907,7 @@
       <c r="N131" s="39"/>
       <c r="O131" s="39"/>
     </row>
-    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
         <v>15</v>
       </c>
@@ -9769,7 +9943,7 @@
       <c r="N132" s="39"/>
       <c r="O132" s="39"/>
     </row>
-    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>15</v>
       </c>
@@ -9805,7 +9979,7 @@
       <c r="N133" s="39"/>
       <c r="O133" s="39"/>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
         <v>15</v>
       </c>
@@ -9841,7 +10015,7 @@
       <c r="N134" s="39"/>
       <c r="O134" s="39"/>
     </row>
-    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>15</v>
       </c>
@@ -9877,7 +10051,7 @@
       <c r="N135" s="39"/>
       <c r="O135" s="39"/>
     </row>
-    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
         <v>15</v>
       </c>
@@ -9913,7 +10087,7 @@
       <c r="N136" s="39"/>
       <c r="O136" s="39"/>
     </row>
-    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
         <v>16</v>
       </c>
@@ -9949,7 +10123,7 @@
       <c r="N137" s="39"/>
       <c r="O137" s="39"/>
     </row>
-    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
         <v>16</v>
       </c>
@@ -9985,7 +10159,7 @@
       <c r="N138" s="39"/>
       <c r="O138" s="39"/>
     </row>
-    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
         <v>16</v>
       </c>
@@ -10021,7 +10195,7 @@
       <c r="N139" s="39"/>
       <c r="O139" s="39"/>
     </row>
-    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
         <v>16</v>
       </c>
@@ -10057,7 +10231,7 @@
       <c r="N140" s="39"/>
       <c r="O140" s="39"/>
     </row>
-    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
         <v>16</v>
       </c>
@@ -10093,7 +10267,7 @@
       <c r="N141" s="39"/>
       <c r="O141" s="39"/>
     </row>
-    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
         <v>16</v>
       </c>
@@ -10129,7 +10303,7 @@
       <c r="N142" s="39"/>
       <c r="O142" s="39"/>
     </row>
-    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
         <v>16</v>
       </c>
@@ -10165,7 +10339,7 @@
       <c r="N143" s="39"/>
       <c r="O143" s="39"/>
     </row>
-    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
         <v>16</v>
       </c>
@@ -10201,7 +10375,7 @@
       <c r="N144" s="39"/>
       <c r="O144" s="39"/>
     </row>
-    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
         <v>16</v>
       </c>
@@ -10237,7 +10411,7 @@
       <c r="N145" s="39"/>
       <c r="O145" s="39"/>
     </row>
-    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
         <v>17</v>
       </c>
@@ -10273,7 +10447,7 @@
       <c r="N146" s="39"/>
       <c r="O146" s="39"/>
     </row>
-    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>17</v>
       </c>
@@ -10309,7 +10483,7 @@
       <c r="N147" s="39"/>
       <c r="O147" s="39"/>
     </row>
-    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>17</v>
       </c>
@@ -10345,7 +10519,7 @@
       <c r="N148" s="39"/>
       <c r="O148" s="39"/>
     </row>
-    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>17</v>
       </c>
@@ -10381,7 +10555,7 @@
       <c r="N149" s="39"/>
       <c r="O149" s="39"/>
     </row>
-    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>17</v>
       </c>
@@ -10417,7 +10591,7 @@
       <c r="N150" s="39"/>
       <c r="O150" s="39"/>
     </row>
-    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
         <v>17</v>
       </c>
@@ -10453,7 +10627,7 @@
       <c r="N151" s="39"/>
       <c r="O151" s="39"/>
     </row>
-    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>17</v>
       </c>
@@ -10489,7 +10663,7 @@
       <c r="N152" s="39"/>
       <c r="O152" s="39"/>
     </row>
-    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>17</v>
       </c>
@@ -10525,7 +10699,7 @@
       <c r="N153" s="39"/>
       <c r="O153" s="39"/>
     </row>
-    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
         <v>17</v>
       </c>
@@ -10561,7 +10735,7 @@
       <c r="N154" s="39"/>
       <c r="O154" s="39"/>
     </row>
-    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>18</v>
       </c>
@@ -10597,7 +10771,7 @@
       <c r="N155" s="39"/>
       <c r="O155" s="39"/>
     </row>
-    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>18</v>
       </c>
@@ -10633,7 +10807,7 @@
       <c r="N156" s="39"/>
       <c r="O156" s="39"/>
     </row>
-    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>18</v>
       </c>
@@ -10669,7 +10843,7 @@
       <c r="N157" s="39"/>
       <c r="O157" s="39"/>
     </row>
-    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
         <v>18</v>
       </c>
@@ -10705,7 +10879,7 @@
       <c r="N158" s="39"/>
       <c r="O158" s="39"/>
     </row>
-    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
         <v>18</v>
       </c>
@@ -10741,7 +10915,7 @@
       <c r="N159" s="39"/>
       <c r="O159" s="39"/>
     </row>
-    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
         <v>18</v>
       </c>
@@ -10777,7 +10951,7 @@
       <c r="N160" s="39"/>
       <c r="O160" s="39"/>
     </row>
-    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>18</v>
       </c>
@@ -10813,7 +10987,7 @@
       <c r="N161" s="39"/>
       <c r="O161" s="39"/>
     </row>
-    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
         <v>18</v>
       </c>
@@ -10849,7 +11023,7 @@
       <c r="N162" s="39"/>
       <c r="O162" s="39"/>
     </row>
-    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>18</v>
       </c>
@@ -10885,7 +11059,7 @@
       <c r="N163" s="39"/>
       <c r="O163" s="39"/>
     </row>
-    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
         <v>19</v>
       </c>
@@ -10921,7 +11095,7 @@
       <c r="N164" s="39"/>
       <c r="O164" s="39"/>
     </row>
-    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
         <v>19</v>
       </c>
@@ -10957,7 +11131,7 @@
       <c r="N165" s="39"/>
       <c r="O165" s="39"/>
     </row>
-    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
         <v>19</v>
       </c>
@@ -10993,7 +11167,7 @@
       <c r="N166" s="39"/>
       <c r="O166" s="39"/>
     </row>
-    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>19</v>
       </c>
@@ -11029,7 +11203,7 @@
       <c r="N167" s="39"/>
       <c r="O167" s="39"/>
     </row>
-    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
         <v>19</v>
       </c>
@@ -11065,7 +11239,7 @@
       <c r="N168" s="39"/>
       <c r="O168" s="39"/>
     </row>
-    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
         <v>19</v>
       </c>
@@ -11101,7 +11275,7 @@
       <c r="N169" s="39"/>
       <c r="O169" s="39"/>
     </row>
-    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
         <v>19</v>
       </c>
@@ -11137,7 +11311,7 @@
       <c r="N170" s="39"/>
       <c r="O170" s="39"/>
     </row>
-    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
         <v>19</v>
       </c>
@@ -11173,7 +11347,7 @@
       <c r="N171" s="39"/>
       <c r="O171" s="39"/>
     </row>
-    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
         <v>19</v>
       </c>
@@ -11209,7 +11383,7 @@
       <c r="N172" s="39"/>
       <c r="O172" s="39"/>
     </row>
-    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
         <v>20</v>
       </c>
@@ -11245,7 +11419,7 @@
       <c r="N173" s="39"/>
       <c r="O173" s="39"/>
     </row>
-    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
         <v>20</v>
       </c>
@@ -11281,7 +11455,7 @@
       <c r="N174" s="39"/>
       <c r="O174" s="39"/>
     </row>
-    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
         <v>20</v>
       </c>
@@ -11317,7 +11491,7 @@
       <c r="N175" s="39"/>
       <c r="O175" s="39"/>
     </row>
-    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
         <v>20</v>
       </c>
@@ -11353,7 +11527,7 @@
       <c r="N176" s="39"/>
       <c r="O176" s="39"/>
     </row>
-    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>20</v>
       </c>
@@ -11389,7 +11563,7 @@
       <c r="N177" s="39"/>
       <c r="O177" s="39"/>
     </row>
-    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
         <v>20</v>
       </c>
@@ -11425,7 +11599,7 @@
       <c r="N178" s="39"/>
       <c r="O178" s="39"/>
     </row>
-    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>20</v>
       </c>
@@ -11461,7 +11635,7 @@
       <c r="N179" s="39"/>
       <c r="O179" s="39"/>
     </row>
-    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>20</v>
       </c>
@@ -11497,7 +11671,7 @@
       <c r="N180" s="39"/>
       <c r="O180" s="39"/>
     </row>
-    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>20</v>
       </c>
@@ -11533,7 +11707,7 @@
       <c r="N181" s="39"/>
       <c r="O181" s="39"/>
     </row>
-    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>21</v>
       </c>
@@ -11569,7 +11743,7 @@
       <c r="N182" s="39"/>
       <c r="O182" s="39"/>
     </row>
-    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>21</v>
       </c>
@@ -11605,7 +11779,7 @@
       <c r="N183" s="39"/>
       <c r="O183" s="39"/>
     </row>
-    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
         <v>21</v>
       </c>
@@ -11641,7 +11815,7 @@
       <c r="N184" s="39"/>
       <c r="O184" s="39"/>
     </row>
-    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>21</v>
       </c>
@@ -11677,7 +11851,7 @@
       <c r="N185" s="39"/>
       <c r="O185" s="39"/>
     </row>
-    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
         <v>21</v>
       </c>
@@ -11713,7 +11887,7 @@
       <c r="N186" s="39"/>
       <c r="O186" s="39"/>
     </row>
-    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>21</v>
       </c>
@@ -11749,7 +11923,7 @@
       <c r="N187" s="39"/>
       <c r="O187" s="39"/>
     </row>
-    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
         <v>21</v>
       </c>
@@ -11785,7 +11959,7 @@
       <c r="N188" s="39"/>
       <c r="O188" s="39"/>
     </row>
-    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
         <v>21</v>
       </c>
@@ -11821,7 +11995,7 @@
       <c r="N189" s="39"/>
       <c r="O189" s="39"/>
     </row>
-    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
         <v>21</v>
       </c>
@@ -11857,7 +12031,7 @@
       <c r="N190" s="39"/>
       <c r="O190" s="39"/>
     </row>
-    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
         <v>22</v>
       </c>
@@ -11893,7 +12067,7 @@
       <c r="N191" s="39"/>
       <c r="O191" s="39"/>
     </row>
-    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
         <v>22</v>
       </c>
@@ -11929,7 +12103,7 @@
       <c r="N192" s="39"/>
       <c r="O192" s="39"/>
     </row>
-    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
         <v>22</v>
       </c>
@@ -11965,7 +12139,7 @@
       <c r="N193" s="39"/>
       <c r="O193" s="39"/>
     </row>
-    <row r="194" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
         <v>22</v>
       </c>
@@ -12001,7 +12175,7 @@
       <c r="N194" s="39"/>
       <c r="O194" s="39"/>
     </row>
-    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
         <v>22</v>
       </c>
@@ -12037,7 +12211,7 @@
       <c r="N195" s="39"/>
       <c r="O195" s="39"/>
     </row>
-    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
         <v>22</v>
       </c>
@@ -12073,7 +12247,7 @@
       <c r="N196" s="39"/>
       <c r="O196" s="39"/>
     </row>
-    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
         <v>22</v>
       </c>
@@ -12109,7 +12283,7 @@
       <c r="N197" s="39"/>
       <c r="O197" s="39"/>
     </row>
-    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
         <v>22</v>
       </c>
@@ -12145,7 +12319,7 @@
       <c r="N198" s="39"/>
       <c r="O198" s="39"/>
     </row>
-    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
         <v>22</v>
       </c>
@@ -12181,7 +12355,7 @@
       <c r="N199" s="39"/>
       <c r="O199" s="39"/>
     </row>
-    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
         <v>23</v>
       </c>
@@ -12217,7 +12391,7 @@
       <c r="N200" s="39"/>
       <c r="O200" s="39"/>
     </row>
-    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
         <v>23</v>
       </c>
@@ -12253,7 +12427,7 @@
       <c r="N201" s="39"/>
       <c r="O201" s="39"/>
     </row>
-    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
         <v>23</v>
       </c>
@@ -12289,7 +12463,7 @@
       <c r="N202" s="39"/>
       <c r="O202" s="39"/>
     </row>
-    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
         <v>23</v>
       </c>
@@ -12325,7 +12499,7 @@
       <c r="N203" s="39"/>
       <c r="O203" s="39"/>
     </row>
-    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
         <v>23</v>
       </c>
@@ -12361,7 +12535,7 @@
       <c r="N204" s="39"/>
       <c r="O204" s="39"/>
     </row>
-    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
         <v>23</v>
       </c>
@@ -12397,7 +12571,7 @@
       <c r="N205" s="39"/>
       <c r="O205" s="39"/>
     </row>
-    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
         <v>23</v>
       </c>
@@ -12433,7 +12607,7 @@
       <c r="N206" s="39"/>
       <c r="O206" s="39"/>
     </row>
-    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
         <v>23</v>
       </c>
@@ -12469,7 +12643,7 @@
       <c r="N207" s="39"/>
       <c r="O207" s="39"/>
     </row>
-    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
         <v>23</v>
       </c>
@@ -12505,7 +12679,7 @@
       <c r="N208" s="39"/>
       <c r="O208" s="39"/>
     </row>
-    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
         <v>24</v>
       </c>
@@ -12541,7 +12715,7 @@
       <c r="N209" s="39"/>
       <c r="O209" s="39"/>
     </row>
-    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
         <v>24</v>
       </c>
@@ -12577,7 +12751,7 @@
       <c r="N210" s="39"/>
       <c r="O210" s="39"/>
     </row>
-    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
         <v>24</v>
       </c>
@@ -12613,7 +12787,7 @@
       <c r="N211" s="39"/>
       <c r="O211" s="39"/>
     </row>
-    <row r="212" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
         <v>24</v>
       </c>
@@ -12649,7 +12823,7 @@
       <c r="N212" s="39"/>
       <c r="O212" s="39"/>
     </row>
-    <row r="213" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
         <v>24</v>
       </c>
@@ -12685,7 +12859,7 @@
       <c r="N213" s="39"/>
       <c r="O213" s="39"/>
     </row>
-    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
         <v>24</v>
       </c>
@@ -12721,7 +12895,7 @@
       <c r="N214" s="39"/>
       <c r="O214" s="39"/>
     </row>
-    <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
         <v>24</v>
       </c>
@@ -12757,7 +12931,7 @@
       <c r="N215" s="39"/>
       <c r="O215" s="39"/>
     </row>
-    <row r="216" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
         <v>24</v>
       </c>
@@ -12793,7 +12967,7 @@
       <c r="N216" s="39"/>
       <c r="O216" s="39"/>
     </row>
-    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
         <v>24</v>
       </c>
@@ -12829,7 +13003,7 @@
       <c r="N217" s="39"/>
       <c r="O217" s="39"/>
     </row>
-    <row r="218" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
         <v>25</v>
       </c>
@@ -12865,7 +13039,7 @@
       <c r="N218" s="39"/>
       <c r="O218" s="39"/>
     </row>
-    <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
         <v>25</v>
       </c>
@@ -12901,7 +13075,7 @@
       <c r="N219" s="39"/>
       <c r="O219" s="39"/>
     </row>
-    <row r="220" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
         <v>25</v>
       </c>
@@ -12937,7 +13111,7 @@
       <c r="N220" s="39"/>
       <c r="O220" s="39"/>
     </row>
-    <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
         <v>25</v>
       </c>
@@ -12973,7 +13147,7 @@
       <c r="N221" s="39"/>
       <c r="O221" s="39"/>
     </row>
-    <row r="222" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
         <v>25</v>
       </c>
@@ -13009,7 +13183,7 @@
       <c r="N222" s="39"/>
       <c r="O222" s="39"/>
     </row>
-    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
         <v>25</v>
       </c>
@@ -13045,7 +13219,7 @@
       <c r="N223" s="39"/>
       <c r="O223" s="39"/>
     </row>
-    <row r="224" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
         <v>25</v>
       </c>
@@ -13081,7 +13255,7 @@
       <c r="N224" s="39"/>
       <c r="O224" s="39"/>
     </row>
-    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
         <v>25</v>
       </c>
@@ -13117,7 +13291,7 @@
       <c r="N225" s="39"/>
       <c r="O225" s="39"/>
     </row>
-    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
         <v>25</v>
       </c>
@@ -13153,7 +13327,7 @@
       <c r="N226" s="39"/>
       <c r="O226" s="39"/>
     </row>
-    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
         <v>26</v>
       </c>
@@ -13189,7 +13363,7 @@
       <c r="N227" s="39"/>
       <c r="O227" s="39"/>
     </row>
-    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
         <v>26</v>
       </c>
@@ -13225,7 +13399,7 @@
       <c r="N228" s="39"/>
       <c r="O228" s="39"/>
     </row>
-    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
         <v>26</v>
       </c>
@@ -13261,7 +13435,7 @@
       <c r="N229" s="39"/>
       <c r="O229" s="39"/>
     </row>
-    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
         <v>26</v>
       </c>
@@ -13297,7 +13471,7 @@
       <c r="N230" s="39"/>
       <c r="O230" s="39"/>
     </row>
-    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
         <v>26</v>
       </c>
@@ -13333,7 +13507,7 @@
       <c r="N231" s="39"/>
       <c r="O231" s="39"/>
     </row>
-    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
         <v>26</v>
       </c>
@@ -13369,7 +13543,7 @@
       <c r="N232" s="39"/>
       <c r="O232" s="39"/>
     </row>
-    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
         <v>26</v>
       </c>
@@ -13405,7 +13579,7 @@
       <c r="N233" s="39"/>
       <c r="O233" s="39"/>
     </row>
-    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
         <v>26</v>
       </c>
@@ -13441,7 +13615,7 @@
       <c r="N234" s="39"/>
       <c r="O234" s="39"/>
     </row>
-    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
         <v>26</v>
       </c>
@@ -13477,7 +13651,7 @@
       <c r="N235" s="39"/>
       <c r="O235" s="39"/>
     </row>
-    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
         <v>27</v>
       </c>
@@ -13513,7 +13687,7 @@
       <c r="N236" s="39"/>
       <c r="O236" s="39"/>
     </row>
-    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
         <v>27</v>
       </c>
@@ -13549,7 +13723,7 @@
       <c r="N237" s="39"/>
       <c r="O237" s="39"/>
     </row>
-    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
         <v>27</v>
       </c>
@@ -13585,7 +13759,7 @@
       <c r="N238" s="39"/>
       <c r="O238" s="39"/>
     </row>
-    <row r="239" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
         <v>27</v>
       </c>
@@ -13621,7 +13795,7 @@
       <c r="N239" s="39"/>
       <c r="O239" s="39"/>
     </row>
-    <row r="240" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
         <v>27</v>
       </c>
@@ -13657,7 +13831,7 @@
       <c r="N240" s="39"/>
       <c r="O240" s="39"/>
     </row>
-    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
         <v>27</v>
       </c>
@@ -13693,7 +13867,7 @@
       <c r="N241" s="39"/>
       <c r="O241" s="39"/>
     </row>
-    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
         <v>27</v>
       </c>
@@ -13729,7 +13903,7 @@
       <c r="N242" s="39"/>
       <c r="O242" s="39"/>
     </row>
-    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
         <v>27</v>
       </c>
@@ -13765,7 +13939,7 @@
       <c r="N243" s="39"/>
       <c r="O243" s="39"/>
     </row>
-    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
         <v>27</v>
       </c>
@@ -13801,7 +13975,7 @@
       <c r="N244" s="39"/>
       <c r="O244" s="39"/>
     </row>
-    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
         <v>28</v>
       </c>
@@ -13837,7 +14011,7 @@
       <c r="N245" s="39"/>
       <c r="O245" s="39"/>
     </row>
-    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
         <v>28</v>
       </c>
@@ -13873,7 +14047,7 @@
       <c r="N246" s="39"/>
       <c r="O246" s="39"/>
     </row>
-    <row r="247" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
         <v>28</v>
       </c>
@@ -13909,7 +14083,7 @@
       <c r="N247" s="39"/>
       <c r="O247" s="39"/>
     </row>
-    <row r="248" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
         <v>28</v>
       </c>
@@ -13945,7 +14119,7 @@
       <c r="N248" s="39"/>
       <c r="O248" s="39"/>
     </row>
-    <row r="249" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
         <v>28</v>
       </c>
@@ -13981,7 +14155,7 @@
       <c r="N249" s="39"/>
       <c r="O249" s="39"/>
     </row>
-    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
         <v>28</v>
       </c>
@@ -14017,7 +14191,7 @@
       <c r="N250" s="39"/>
       <c r="O250" s="39"/>
     </row>
-    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
         <v>28</v>
       </c>
@@ -14053,7 +14227,7 @@
       <c r="N251" s="39"/>
       <c r="O251" s="39"/>
     </row>
-    <row r="252" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
         <v>28</v>
       </c>
@@ -14089,7 +14263,7 @@
       <c r="N252" s="39"/>
       <c r="O252" s="39"/>
     </row>
-    <row r="253" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
         <v>28</v>
       </c>
@@ -14125,7 +14299,7 @@
       <c r="N253" s="39"/>
       <c r="O253" s="39"/>
     </row>
-    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A254" s="4">
         <v>29</v>
       </c>
@@ -14161,7 +14335,7 @@
       <c r="N254" s="39"/>
       <c r="O254" s="39"/>
     </row>
-    <row r="255" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
         <v>29</v>
       </c>
@@ -14197,7 +14371,7 @@
       <c r="N255" s="39"/>
       <c r="O255" s="39"/>
     </row>
-    <row r="256" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
         <v>29</v>
       </c>
@@ -14233,7 +14407,7 @@
       <c r="N256" s="39"/>
       <c r="O256" s="39"/>
     </row>
-    <row r="257" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
         <v>29</v>
       </c>
@@ -14269,7 +14443,7 @@
       <c r="N257" s="39"/>
       <c r="O257" s="39"/>
     </row>
-    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
         <v>29</v>
       </c>
@@ -14305,7 +14479,7 @@
       <c r="N258" s="39"/>
       <c r="O258" s="39"/>
     </row>
-    <row r="259" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
         <v>29</v>
       </c>
@@ -14341,7 +14515,7 @@
       <c r="N259" s="39"/>
       <c r="O259" s="39"/>
     </row>
-    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
         <v>29</v>
       </c>
@@ -14377,7 +14551,7 @@
       <c r="N260" s="39"/>
       <c r="O260" s="39"/>
     </row>
-    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
         <v>29</v>
       </c>
@@ -14413,7 +14587,7 @@
       <c r="N261" s="39"/>
       <c r="O261" s="39"/>
     </row>
-    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
         <v>29</v>
       </c>
@@ -14449,7 +14623,7 @@
       <c r="N262" s="39"/>
       <c r="O262" s="39"/>
     </row>
-    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
         <v>30</v>
       </c>
@@ -14485,7 +14659,7 @@
       <c r="N263" s="39"/>
       <c r="O263" s="39"/>
     </row>
-    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A264" s="4">
         <v>30</v>
       </c>
@@ -14521,7 +14695,7 @@
       <c r="N264" s="39"/>
       <c r="O264" s="39"/>
     </row>
-    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
         <v>30</v>
       </c>
@@ -14557,7 +14731,7 @@
       <c r="N265" s="39"/>
       <c r="O265" s="39"/>
     </row>
-    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A266" s="4">
         <v>30</v>
       </c>
@@ -14593,7 +14767,7 @@
       <c r="N266" s="39"/>
       <c r="O266" s="39"/>
     </row>
-    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A267" s="4">
         <v>30</v>
       </c>
@@ -14629,7 +14803,7 @@
       <c r="N267" s="39"/>
       <c r="O267" s="39"/>
     </row>
-    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A268" s="4">
         <v>30</v>
       </c>
@@ -14665,7 +14839,7 @@
       <c r="N268" s="39"/>
       <c r="O268" s="39"/>
     </row>
-    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A269" s="4">
         <v>30</v>
       </c>
@@ -14701,7 +14875,7 @@
       <c r="N269" s="39"/>
       <c r="O269" s="39"/>
     </row>
-    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A270" s="4">
         <v>30</v>
       </c>
@@ -14737,7 +14911,7 @@
       <c r="N270" s="39"/>
       <c r="O270" s="39"/>
     </row>
-    <row r="271" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A271" s="4">
         <v>30</v>
       </c>
@@ -14773,7 +14947,7 @@
       <c r="N271" s="39"/>
       <c r="O271" s="39"/>
     </row>
-    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A272" s="4">
         <v>31</v>
       </c>
@@ -14809,7 +14983,7 @@
       <c r="N272" s="39"/>
       <c r="O272" s="39"/>
     </row>
-    <row r="273" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273" s="4">
         <v>31</v>
       </c>
@@ -14845,7 +15019,7 @@
       <c r="N273" s="39"/>
       <c r="O273" s="39"/>
     </row>
-    <row r="274" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274" s="4">
         <v>31</v>
       </c>
@@ -14881,7 +15055,7 @@
       <c r="N274" s="39"/>
       <c r="O274" s="39"/>
     </row>
-    <row r="275" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275" s="4">
         <v>31</v>
       </c>
@@ -14917,7 +15091,7 @@
       <c r="N275" s="39"/>
       <c r="O275" s="39"/>
     </row>
-    <row r="276" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276" s="4">
         <v>31</v>
       </c>
@@ -14953,7 +15127,7 @@
       <c r="N276" s="39"/>
       <c r="O276" s="39"/>
     </row>
-    <row r="277" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A277" s="4">
         <v>31</v>
       </c>
@@ -14989,7 +15163,7 @@
       <c r="N277" s="39"/>
       <c r="O277" s="39"/>
     </row>
-    <row r="278" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278" s="4">
         <v>31</v>
       </c>
@@ -15025,7 +15199,7 @@
       <c r="N278" s="39"/>
       <c r="O278" s="39"/>
     </row>
-    <row r="279" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279" s="4">
         <v>31</v>
       </c>
@@ -15061,7 +15235,7 @@
       <c r="N279" s="39"/>
       <c r="O279" s="39"/>
     </row>
-    <row r="280" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280" s="4">
         <v>31</v>
       </c>
@@ -15097,7 +15271,7 @@
       <c r="N280" s="39"/>
       <c r="O280" s="39"/>
     </row>
-    <row r="281" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
         <v>32</v>
       </c>
@@ -15133,7 +15307,7 @@
       <c r="N281" s="39"/>
       <c r="O281" s="39"/>
     </row>
-    <row r="282" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A282" s="4">
         <v>32</v>
       </c>
@@ -15169,7 +15343,7 @@
       <c r="N282" s="39"/>
       <c r="O282" s="39"/>
     </row>
-    <row r="283" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" s="4">
         <v>32</v>
       </c>
@@ -15205,7 +15379,7 @@
       <c r="N283" s="39"/>
       <c r="O283" s="39"/>
     </row>
-    <row r="284" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284" s="4">
         <v>32</v>
       </c>
@@ -15241,7 +15415,7 @@
       <c r="N284" s="39"/>
       <c r="O284" s="39"/>
     </row>
-    <row r="285" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
         <v>32</v>
       </c>
@@ -15277,7 +15451,7 @@
       <c r="N285" s="39"/>
       <c r="O285" s="39"/>
     </row>
-    <row r="286" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286" s="4">
         <v>32</v>
       </c>
@@ -15313,7 +15487,7 @@
       <c r="N286" s="39"/>
       <c r="O286" s="39"/>
     </row>
-    <row r="287" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A287" s="4">
         <v>32</v>
       </c>
@@ -15349,7 +15523,7 @@
       <c r="N287" s="39"/>
       <c r="O287" s="39"/>
     </row>
-    <row r="288" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A288" s="4">
         <v>32</v>
       </c>
@@ -15385,7 +15559,7 @@
       <c r="N288" s="39"/>
       <c r="O288" s="39"/>
     </row>
-    <row r="289" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" s="4">
         <v>32</v>
       </c>
@@ -15421,7 +15595,7 @@
       <c r="N289" s="39"/>
       <c r="O289" s="39"/>
     </row>
-    <row r="290" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" s="4">
         <v>33</v>
       </c>
@@ -15457,7 +15631,7 @@
       <c r="N290" s="39"/>
       <c r="O290" s="39"/>
     </row>
-    <row r="291" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" s="4">
         <v>33</v>
       </c>
@@ -15493,7 +15667,7 @@
       <c r="N291" s="39"/>
       <c r="O291" s="39"/>
     </row>
-    <row r="292" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A292" s="4">
         <v>33</v>
       </c>
@@ -15529,7 +15703,7 @@
       <c r="N292" s="39"/>
       <c r="O292" s="39"/>
     </row>
-    <row r="293" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A293" s="4">
         <v>33</v>
       </c>
@@ -15565,7 +15739,7 @@
       <c r="N293" s="39"/>
       <c r="O293" s="39"/>
     </row>
-    <row r="294" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A294" s="4">
         <v>33</v>
       </c>
@@ -15601,7 +15775,7 @@
       <c r="N294" s="39"/>
       <c r="O294" s="39"/>
     </row>
-    <row r="295" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
         <v>33</v>
       </c>
@@ -15637,7 +15811,7 @@
       <c r="N295" s="39"/>
       <c r="O295" s="39"/>
     </row>
-    <row r="296" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A296" s="4">
         <v>33</v>
       </c>
@@ -15673,7 +15847,7 @@
       <c r="N296" s="39"/>
       <c r="O296" s="39"/>
     </row>
-    <row r="297" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A297" s="4">
         <v>33</v>
       </c>
@@ -15709,7 +15883,7 @@
       <c r="N297" s="39"/>
       <c r="O297" s="39"/>
     </row>
-    <row r="298" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A298" s="4">
         <v>33</v>
       </c>
@@ -15745,7 +15919,7 @@
       <c r="N298" s="39"/>
       <c r="O298" s="39"/>
     </row>
-    <row r="299" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
         <v>34</v>
       </c>
@@ -15781,7 +15955,7 @@
       <c r="N299" s="39"/>
       <c r="O299" s="39"/>
     </row>
-    <row r="300" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A300" s="4">
         <v>34</v>
       </c>
@@ -15817,7 +15991,7 @@
       <c r="N300" s="39"/>
       <c r="O300" s="39"/>
     </row>
-    <row r="301" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
         <v>34</v>
       </c>
@@ -15853,7 +16027,7 @@
       <c r="N301" s="39"/>
       <c r="O301" s="39"/>
     </row>
-    <row r="302" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
         <v>34</v>
       </c>
@@ -15889,7 +16063,7 @@
       <c r="N302" s="39"/>
       <c r="O302" s="39"/>
     </row>
-    <row r="303" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
         <v>34</v>
       </c>
@@ -15925,7 +16099,7 @@
       <c r="N303" s="39"/>
       <c r="O303" s="39"/>
     </row>
-    <row r="304" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A304" s="4">
         <v>34</v>
       </c>
@@ -15961,7 +16135,7 @@
       <c r="N304" s="39"/>
       <c r="O304" s="39"/>
     </row>
-    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A305" s="4">
         <v>34</v>
       </c>
@@ -15997,7 +16171,7 @@
       <c r="N305" s="39"/>
       <c r="O305" s="39"/>
     </row>
-    <row r="306" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A306" s="4">
         <v>34</v>
       </c>
@@ -16033,7 +16207,7 @@
       <c r="N306" s="39"/>
       <c r="O306" s="39"/>
     </row>
-    <row r="307" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A307" s="4">
         <v>34</v>
       </c>
@@ -16079,7 +16253,7 @@
       </c>
       <c r="C308" s="24">
         <f>SUBTOTAL(101,Table4[Start Time])</f>
-        <v>0.62268518518518512</v>
+        <v>0.63051470588235314</v>
       </c>
       <c r="D308" s="24"/>
       <c r="E308" s="24"/>
@@ -16087,24 +16261,24 @@
       <c r="G308" s="3"/>
       <c r="H308" s="22">
         <f>SUBTOTAL(103,Table4[Venue])</f>
-        <v>9</v>
+        <v>306</v>
       </c>
       <c r="I308" s="23">
         <f>SUBTOTAL(101,Table4[Capacity])</f>
-        <v>46411.111111111109</v>
+        <v>51816.666666666664</v>
       </c>
       <c r="J308" s="38">
         <f>SUBTOTAL(101,Table4[Attendance])</f>
-        <v>40230.222222222219</v>
+        <v>43511.666666666664</v>
       </c>
       <c r="K308" s="1"/>
       <c r="L308" s="37">
         <f>SUBTOTAL(101,Table4[TICKET PRICE])</f>
-        <v>43.237777777777779</v>
+        <v>43.129777777777768</v>
       </c>
       <c r="M308" s="37">
         <f>SUBTOTAL(109,Table4[MATCH REVENUE])</f>
-        <v>16797920.77</v>
+        <v>92370683.020000011</v>
       </c>
       <c r="N308" s="3"/>
       <c r="O308" s="3"/>
@@ -16275,7 +16449,7 @@
       </c>
       <c r="R2" s="4">
         <f t="shared" ref="R2:R71" ca="1" si="3">DATEDIF(TODAY(),O2,"m")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
@@ -16345,7 +16519,7 @@
       </c>
       <c r="R3" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
@@ -16415,7 +16589,7 @@
       </c>
       <c r="R4" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
@@ -16485,7 +16659,7 @@
       </c>
       <c r="R5" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
@@ -16557,7 +16731,7 @@
       </c>
       <c r="R6" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
@@ -16595,7 +16769,7 @@
       </c>
       <c r="I7" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J7" s="8">
         <v>45000000</v>
@@ -16627,7 +16801,7 @@
       </c>
       <c r="R7" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
@@ -16697,7 +16871,7 @@
       </c>
       <c r="R8" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
@@ -16767,7 +16941,7 @@
       </c>
       <c r="R9" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
@@ -16837,7 +17011,7 @@
       </c>
       <c r="R10" s="4">
         <f ca="1">DATEDIF(TODAY(),O10,"m")</f>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
@@ -16907,7 +17081,7 @@
       </c>
       <c r="R11" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
@@ -16977,7 +17151,7 @@
       </c>
       <c r="R12" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
@@ -17047,7 +17221,7 @@
       </c>
       <c r="R13" s="4">
         <f ca="1">DATEDIF(TODAY(),O13,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
@@ -17117,7 +17291,7 @@
       </c>
       <c r="R14" s="4">
         <f ca="1">DATEDIF(TODAY(),O14,"m")</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
@@ -17155,7 +17329,7 @@
       </c>
       <c r="I15" s="21">
         <f ca="1">DATEDIF(H15,TODAY(),"Y")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" s="8">
         <v>85000000</v>
@@ -17187,7 +17361,7 @@
       </c>
       <c r="R15" s="4">
         <f ca="1">DATEDIF(TODAY(),O15,"m")</f>
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
@@ -17257,7 +17431,7 @@
       </c>
       <c r="R16" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
@@ -17327,7 +17501,7 @@
       </c>
       <c r="R17" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
@@ -17397,7 +17571,7 @@
       </c>
       <c r="R18" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
@@ -17469,7 +17643,7 @@
       </c>
       <c r="R19" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
@@ -17539,7 +17713,7 @@
       </c>
       <c r="R20" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
@@ -17577,7 +17751,7 @@
       </c>
       <c r="I21" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J21" s="8">
         <v>10000000</v>
@@ -17609,7 +17783,7 @@
       </c>
       <c r="R21" s="4">
         <f t="shared" ref="R21" ca="1" si="6">DATEDIF(TODAY(),O21,"m")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
@@ -17679,7 +17853,7 @@
       </c>
       <c r="R22" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S22" s="4"/>
       <c r="T22" s="4"/>
@@ -17749,7 +17923,7 @@
       </c>
       <c r="R23" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S23" s="4"/>
       <c r="T23" s="4"/>
@@ -17819,7 +17993,7 @@
       </c>
       <c r="R24" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
@@ -17889,7 +18063,7 @@
       </c>
       <c r="R25" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
@@ -17959,7 +18133,7 @@
       </c>
       <c r="R26" s="4">
         <f ca="1">DATEDIF(TODAY(),O26,"m")</f>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S26" s="4"/>
       <c r="T26" s="4"/>
@@ -18029,7 +18203,7 @@
       </c>
       <c r="R27" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S27" s="4"/>
       <c r="T27" s="4"/>
@@ -18097,7 +18271,7 @@
       </c>
       <c r="R28" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
@@ -18165,7 +18339,7 @@
       </c>
       <c r="R29" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S29" s="4"/>
       <c r="T29" s="4"/>
@@ -18233,7 +18407,7 @@
       </c>
       <c r="R30" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S30" s="4"/>
       <c r="T30" s="4"/>
@@ -18301,7 +18475,7 @@
       </c>
       <c r="R31" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S31" s="4"/>
       <c r="T31" s="4"/>
@@ -18369,7 +18543,7 @@
       </c>
       <c r="R32" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S32" s="4"/>
       <c r="T32" s="4"/>
@@ -18439,7 +18613,7 @@
       </c>
       <c r="R33" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
@@ -18509,7 +18683,7 @@
       </c>
       <c r="R34" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
@@ -18547,7 +18721,7 @@
       </c>
       <c r="I35" s="21">
         <f ca="1">DATEDIF(H35,TODAY(),"Y")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J35" s="8">
         <v>16000000</v>
@@ -18579,7 +18753,7 @@
       </c>
       <c r="R35" s="4">
         <f ca="1">DATEDIF(TODAY(),O35,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S35" s="4"/>
       <c r="T35" s="4"/>
@@ -18649,7 +18823,7 @@
       </c>
       <c r="R36" s="4">
         <f ca="1">DATEDIF(TODAY(),O36,"m")</f>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S36" s="4"/>
       <c r="T36" s="4"/>
@@ -18717,7 +18891,7 @@
       </c>
       <c r="R37" s="4">
         <f ca="1">DATEDIF(TODAY(),O37,"m")</f>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S37" s="4"/>
       <c r="T37" s="4"/>
@@ -18787,7 +18961,7 @@
       </c>
       <c r="R38" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S38" s="4"/>
       <c r="T38" s="4"/>
@@ -18855,7 +19029,7 @@
       </c>
       <c r="R39" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S39" s="4"/>
       <c r="T39" s="4"/>
@@ -18923,7 +19097,7 @@
       </c>
       <c r="R40" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S40" s="4"/>
       <c r="T40" s="4"/>
@@ -18993,7 +19167,7 @@
       </c>
       <c r="R41" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S41" s="4"/>
       <c r="T41" s="4"/>
@@ -19063,7 +19237,7 @@
       </c>
       <c r="R42" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S42" s="4"/>
       <c r="T42" s="4"/>
@@ -19109,7 +19283,7 @@
         <v>131000000</v>
       </c>
       <c r="K43" s="8">
-        <v>75000000</v>
+        <v>90000000</v>
       </c>
       <c r="L43" s="8">
         <v>450000</v>
@@ -19135,7 +19309,7 @@
       </c>
       <c r="R43" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S43" s="4"/>
       <c r="T43" s="4"/>
@@ -19205,7 +19379,7 @@
       </c>
       <c r="R44" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S44" s="4"/>
       <c r="T44" s="4"/>
@@ -19273,7 +19447,7 @@
       </c>
       <c r="R45" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S45" s="4"/>
       <c r="T45" s="4"/>
@@ -19343,7 +19517,7 @@
       </c>
       <c r="R46" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S46" s="4"/>
       <c r="T46" s="4"/>
@@ -19411,7 +19585,7 @@
       </c>
       <c r="R47" s="4">
         <f ca="1">DATEDIF(TODAY(),O47,"m")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S47" s="4"/>
       <c r="T47" s="4"/>
@@ -19481,7 +19655,7 @@
       </c>
       <c r="R48" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S48" s="4"/>
       <c r="T48" s="4"/>
@@ -19551,7 +19725,7 @@
       </c>
       <c r="R49" s="4">
         <f ca="1">DATEDIF(TODAY(),O49,"m")</f>
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="S49" s="4"/>
       <c r="T49" s="4"/>
@@ -19621,7 +19795,7 @@
       </c>
       <c r="R50" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S50" s="4"/>
       <c r="T50" s="4"/>
@@ -19689,7 +19863,7 @@
       </c>
       <c r="R51" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S51" s="4"/>
       <c r="T51" s="4"/>
@@ -19759,7 +19933,7 @@
       </c>
       <c r="R52" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S52" s="4"/>
       <c r="T52" s="4"/>
@@ -19827,7 +20001,7 @@
       </c>
       <c r="R53" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S53" s="4"/>
       <c r="T53" s="4"/>
@@ -19897,7 +20071,7 @@
       </c>
       <c r="R54" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S54" s="4"/>
       <c r="T54" s="4"/>
@@ -19967,7 +20141,7 @@
       </c>
       <c r="R55" s="4">
         <f ca="1">DATEDIF(TODAY(),O55,"m")</f>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S55" s="4"/>
       <c r="T55" s="4"/>
@@ -20037,7 +20211,7 @@
       </c>
       <c r="R56" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S56" s="4"/>
       <c r="T56" s="4"/>
@@ -20107,7 +20281,7 @@
       </c>
       <c r="R57" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S57" s="4"/>
       <c r="T57" s="4"/>
@@ -20177,7 +20351,7 @@
       </c>
       <c r="R58" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S58" s="4"/>
       <c r="T58" s="4"/>
@@ -20247,7 +20421,7 @@
       </c>
       <c r="R59" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S59" s="4"/>
       <c r="T59" s="4"/>
@@ -20317,7 +20491,7 @@
       </c>
       <c r="R60" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S60" s="4"/>
       <c r="T60" s="4"/>
@@ -20387,7 +20561,7 @@
       </c>
       <c r="R61" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S61" s="4"/>
       <c r="T61" s="4"/>
@@ -20457,7 +20631,7 @@
       </c>
       <c r="R62" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S62" s="4"/>
       <c r="T62" s="4"/>
@@ -20527,7 +20701,7 @@
       </c>
       <c r="R63" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S63" s="4"/>
       <c r="T63" s="4"/>
@@ -20597,7 +20771,7 @@
       </c>
       <c r="R64" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S64" s="4"/>
       <c r="T64" s="4"/>
@@ -20635,7 +20809,7 @@
       </c>
       <c r="I65" s="21">
         <f ca="1">DATEDIF(H65,TODAY(),"Y")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J65" s="8">
         <v>0</v>
@@ -20667,7 +20841,7 @@
       </c>
       <c r="R65" s="4">
         <f ca="1">DATEDIF(TODAY(),O65,"m")</f>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S65" s="4"/>
       <c r="T65" s="4"/>
@@ -20737,7 +20911,7 @@
       </c>
       <c r="R66" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S66" s="4"/>
       <c r="T66" s="4"/>
@@ -20807,7 +20981,7 @@
       </c>
       <c r="R67" s="4">
         <f ca="1">DATEDIF(TODAY(),O67,"m")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S67" s="4"/>
       <c r="T67" s="4"/>
@@ -20875,7 +21049,7 @@
       </c>
       <c r="R68" s="4">
         <f ca="1">DATEDIF(TODAY(),O68,"m")</f>
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="S68" s="4"/>
       <c r="T68" s="4"/>
@@ -20943,7 +21117,7 @@
       </c>
       <c r="R69" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S69" s="4"/>
       <c r="T69" s="4"/>
@@ -21015,7 +21189,7 @@
       </c>
       <c r="R70" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S70" s="4"/>
       <c r="T70" s="4"/>
@@ -21085,7 +21259,7 @@
       </c>
       <c r="R71" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S71" s="4"/>
       <c r="T71" s="4"/>
@@ -21155,7 +21329,7 @@
       </c>
       <c r="R72" s="4">
         <f t="shared" ref="R72" ca="1" si="9">DATEDIF(TODAY(),O72,"m")</f>
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="S72" s="4"/>
       <c r="T72" s="4"/>
@@ -21225,7 +21399,7 @@
       </c>
       <c r="R73" s="4">
         <f t="shared" ref="R73:R138" ca="1" si="13">DATEDIF(TODAY(),O73,"m")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S73" s="4"/>
       <c r="T73" s="4"/>
@@ -21295,7 +21469,7 @@
       </c>
       <c r="R74" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S74" s="4"/>
       <c r="T74" s="4"/>
@@ -21328,14 +21502,14 @@
         <v>35</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H75" s="7">
         <v>33871</v>
       </c>
       <c r="I75" s="21">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J75" s="8">
         <v>0</v>
@@ -21367,7 +21541,7 @@
       </c>
       <c r="R75" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S75" s="4"/>
       <c r="T75" s="4"/>
@@ -21437,7 +21611,7 @@
       </c>
       <c r="R76" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S76" s="4"/>
       <c r="T76" s="4"/>
@@ -21475,7 +21649,7 @@
       </c>
       <c r="I77" s="21">
         <f t="shared" ca="1" si="10"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J77" s="8">
         <v>0</v>
@@ -21507,7 +21681,7 @@
       </c>
       <c r="R77" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S77" s="4"/>
       <c r="T77" s="4"/>
@@ -21575,7 +21749,7 @@
       </c>
       <c r="R78" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S78" s="4"/>
       <c r="T78" s="4"/>
@@ -21645,7 +21819,7 @@
       </c>
       <c r="R79" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S79" s="4"/>
       <c r="T79" s="4"/>
@@ -21715,7 +21889,7 @@
       </c>
       <c r="R80" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S80" s="4"/>
       <c r="T80" s="4"/>
@@ -21785,7 +21959,7 @@
       </c>
       <c r="R81" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S81" s="4"/>
       <c r="T81" s="4"/>
@@ -21855,7 +22029,7 @@
       </c>
       <c r="R82" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S82" s="4"/>
       <c r="T82" s="4"/>
@@ -21925,7 +22099,7 @@
       </c>
       <c r="R83" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S83" s="4"/>
       <c r="T83" s="4"/>
@@ -21995,7 +22169,7 @@
       </c>
       <c r="R84" s="4">
         <f ca="1">DATEDIF(TODAY(),O84,"m")</f>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S84" s="4"/>
       <c r="T84" s="4"/>
@@ -22065,7 +22239,7 @@
       </c>
       <c r="R85" s="4">
         <f ca="1">DATEDIF(TODAY(),O85,"m")</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S85" s="4"/>
       <c r="T85" s="4"/>
@@ -22135,7 +22309,7 @@
       </c>
       <c r="R86" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S86" s="4"/>
       <c r="T86" s="4"/>
@@ -22205,7 +22379,7 @@
       </c>
       <c r="R87" s="4">
         <f ca="1">DATEDIF(TODAY(),O87,"m")</f>
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="S87" s="4"/>
       <c r="T87" s="4"/>
@@ -22275,7 +22449,7 @@
       </c>
       <c r="R88" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S88" s="4"/>
       <c r="T88" s="4"/>
@@ -22345,7 +22519,7 @@
       </c>
       <c r="R89" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S89" s="4"/>
       <c r="T89" s="4"/>
@@ -22413,7 +22587,7 @@
       </c>
       <c r="R90" s="4">
         <f ca="1">DATEDIF(TODAY(),O90,"m")</f>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S90" s="4"/>
       <c r="T90" s="4"/>
@@ -22442,7 +22616,7 @@
         <v>29</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H91" s="7">
         <v>36776</v>
@@ -22481,7 +22655,7 @@
       </c>
       <c r="R91" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S91" s="4"/>
       <c r="T91" s="4"/>
@@ -22551,7 +22725,7 @@
       </c>
       <c r="R92" s="4">
         <f ca="1">DATEDIF(TODAY(),O92,"m")</f>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S92" s="4"/>
       <c r="T92" s="4"/>
@@ -22619,7 +22793,7 @@
       </c>
       <c r="R93" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S93" s="4"/>
       <c r="T93" s="4"/>
@@ -22691,7 +22865,7 @@
       </c>
       <c r="R94" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S94" s="4"/>
       <c r="T94" s="4"/>
@@ -22761,7 +22935,7 @@
       </c>
       <c r="R95" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S95" s="4"/>
       <c r="T95" s="4"/>
@@ -22829,7 +23003,7 @@
       </c>
       <c r="R96" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S96" s="4"/>
       <c r="T96" s="4"/>
@@ -22899,7 +23073,7 @@
       </c>
       <c r="R97" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S97" s="4"/>
       <c r="T97" s="4"/>
@@ -22969,7 +23143,7 @@
       </c>
       <c r="R98" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S98" s="4"/>
       <c r="T98" s="4"/>
@@ -23037,7 +23211,7 @@
       </c>
       <c r="R99" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S99" s="4"/>
       <c r="T99" s="4"/>
@@ -23107,7 +23281,7 @@
       </c>
       <c r="R100" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S100" s="4"/>
       <c r="T100" s="4"/>
@@ -23177,7 +23351,7 @@
       </c>
       <c r="R101" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S101" s="4"/>
       <c r="T101" s="4"/>
@@ -23245,7 +23419,7 @@
       </c>
       <c r="R102" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S102" s="4"/>
       <c r="T102" s="4"/>
@@ -23313,7 +23487,7 @@
       </c>
       <c r="R103" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S103" s="4"/>
       <c r="T103" s="4"/>
@@ -23351,7 +23525,7 @@
       </c>
       <c r="I104" s="21">
         <f t="shared" ca="1" si="10"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J104" s="8">
         <v>110000000</v>
@@ -23383,7 +23557,7 @@
       </c>
       <c r="R104" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S104" s="4"/>
       <c r="T104" s="4"/>
@@ -23453,7 +23627,7 @@
       </c>
       <c r="R105" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S105" s="4"/>
       <c r="T105" s="4"/>
@@ -23521,7 +23695,7 @@
       </c>
       <c r="R106" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S106" s="4"/>
       <c r="T106" s="4"/>
@@ -23591,7 +23765,7 @@
       </c>
       <c r="R107" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S107" s="4"/>
       <c r="T107" s="4"/>
@@ -23661,7 +23835,7 @@
       </c>
       <c r="R108" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S108" s="4"/>
       <c r="T108" s="4"/>
@@ -23731,7 +23905,7 @@
       </c>
       <c r="R109" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S109" s="4"/>
       <c r="T109" s="4"/>
@@ -23801,7 +23975,7 @@
       </c>
       <c r="R110" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S110" s="4"/>
       <c r="T110" s="4"/>
@@ -23871,7 +24045,7 @@
       </c>
       <c r="R111" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S111" s="4"/>
       <c r="T111" s="4"/>
@@ -23941,7 +24115,7 @@
       </c>
       <c r="R112" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S112" s="4"/>
       <c r="T112" s="4"/>
@@ -24011,7 +24185,7 @@
       </c>
       <c r="R113" s="4">
         <f ca="1">DATEDIF(TODAY(),O113,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S113" s="4"/>
       <c r="T113" s="4"/>
@@ -24081,7 +24255,7 @@
       </c>
       <c r="R114" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S114" s="4"/>
       <c r="T114" s="4"/>
@@ -24151,7 +24325,7 @@
       </c>
       <c r="R115" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S115" s="4"/>
       <c r="T115" s="4"/>
@@ -24219,7 +24393,7 @@
       </c>
       <c r="R116" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S116" s="4"/>
       <c r="T116" s="4"/>
@@ -24287,7 +24461,7 @@
       </c>
       <c r="R117" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S117" s="4"/>
       <c r="T117" s="4"/>
@@ -24359,7 +24533,7 @@
       </c>
       <c r="R118" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S118" s="4"/>
       <c r="T118" s="4"/>
@@ -24429,7 +24603,7 @@
       </c>
       <c r="R119" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S119" s="4"/>
       <c r="T119" s="4"/>
@@ -24467,7 +24641,7 @@
       </c>
       <c r="I120" s="21">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J120" s="8">
         <v>0</v>
@@ -24499,7 +24673,7 @@
       </c>
       <c r="R120" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S120" s="4"/>
       <c r="T120" s="4"/>
@@ -24569,7 +24743,7 @@
       </c>
       <c r="R121" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S121" s="4"/>
       <c r="T121" s="4"/>
@@ -24639,7 +24813,7 @@
       </c>
       <c r="R122" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S122" s="4"/>
       <c r="T122" s="4"/>
@@ -24709,7 +24883,7 @@
       </c>
       <c r="R123" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S123" s="4"/>
       <c r="T123" s="4"/>
@@ -24779,7 +24953,7 @@
       </c>
       <c r="R124" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S124" s="4"/>
       <c r="T124" s="4"/>
@@ -24849,7 +25023,7 @@
       </c>
       <c r="R125" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S125" s="4"/>
       <c r="T125" s="4"/>
@@ -24917,7 +25091,7 @@
       </c>
       <c r="R126" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S126" s="4"/>
       <c r="T126" s="4"/>
@@ -24985,7 +25159,7 @@
       </c>
       <c r="R127" s="4">
         <f ca="1">DATEDIF(TODAY(),O127,"m")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S127" s="4"/>
       <c r="T127" s="4"/>
@@ -25053,7 +25227,7 @@
       </c>
       <c r="R128" s="4">
         <f ca="1">DATEDIF(TODAY(),O128,"m")</f>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S128" s="4"/>
       <c r="T128" s="4"/>
@@ -25123,7 +25297,7 @@
       </c>
       <c r="R129" s="4">
         <f ca="1">DATEDIF(TODAY(),O129,"m")</f>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S129" s="4"/>
       <c r="T129" s="4"/>
@@ -25193,7 +25367,7 @@
       </c>
       <c r="R130" s="4">
         <f ca="1">DATEDIF(TODAY(),O130,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S130" s="4"/>
       <c r="T130" s="4"/>
@@ -25263,7 +25437,7 @@
       </c>
       <c r="R131" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S131" s="4"/>
       <c r="T131" s="4"/>
@@ -25325,7 +25499,7 @@
       </c>
       <c r="P132" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q132" s="4">
         <f t="shared" ca="1" si="12"/>
@@ -25333,7 +25507,7 @@
       </c>
       <c r="R132" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S132" s="4"/>
       <c r="T132" s="4"/>
@@ -25403,7 +25577,7 @@
       </c>
       <c r="R133" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S133" s="4"/>
       <c r="T133" s="4"/>
@@ -25473,7 +25647,7 @@
       </c>
       <c r="R134" s="4">
         <f ca="1">DATEDIF(TODAY(),O134,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S134" s="4"/>
       <c r="T134" s="4"/>
@@ -25543,7 +25717,7 @@
       </c>
       <c r="R135" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S135" s="4"/>
       <c r="T135" s="4"/>
@@ -25613,7 +25787,7 @@
       </c>
       <c r="R136" s="4">
         <f ca="1">DATEDIF(TODAY(),O136,"m")</f>
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S136" s="4"/>
       <c r="T136" s="4"/>
@@ -25683,7 +25857,7 @@
       </c>
       <c r="R137" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S137" s="4"/>
       <c r="T137" s="4"/>
@@ -25753,7 +25927,7 @@
       </c>
       <c r="R138" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S138" s="4"/>
       <c r="T138" s="4"/>
@@ -25823,7 +25997,7 @@
       </c>
       <c r="R139" s="4">
         <f t="shared" ref="R139:R204" ca="1" si="17">DATEDIF(TODAY(),O139,"m")</f>
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="S139" s="4"/>
       <c r="T139" s="4"/>
@@ -25893,7 +26067,7 @@
       </c>
       <c r="R140" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S140" s="4"/>
       <c r="T140" s="4"/>
@@ -25955,7 +26129,7 @@
       </c>
       <c r="P141" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q141" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -25963,7 +26137,7 @@
       </c>
       <c r="R141" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S141" s="4"/>
       <c r="T141" s="4"/>
@@ -26033,7 +26207,7 @@
       </c>
       <c r="R142" s="4">
         <f ca="1">DATEDIF(TODAY(),O142,"m")</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S142" s="4"/>
       <c r="T142" s="4"/>
@@ -26103,7 +26277,7 @@
       </c>
       <c r="R143" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S143" s="4"/>
       <c r="T143" s="4"/>
@@ -26173,7 +26347,7 @@
       </c>
       <c r="R144" s="4">
         <f ca="1">DATEDIF(TODAY(),O144,"m")</f>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S144" s="4"/>
       <c r="T144" s="4"/>
@@ -26243,7 +26417,7 @@
       </c>
       <c r="R145" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S145" s="4"/>
       <c r="T145" s="4"/>
@@ -26313,7 +26487,7 @@
       </c>
       <c r="R146" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S146" s="4"/>
       <c r="T146" s="4"/>
@@ -26383,7 +26557,7 @@
       </c>
       <c r="R147" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S147" s="4"/>
       <c r="T147" s="4"/>
@@ -26453,7 +26627,7 @@
       </c>
       <c r="R148" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S148" s="4"/>
       <c r="T148" s="4"/>
@@ -26525,7 +26699,7 @@
       </c>
       <c r="R149" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S149" s="4"/>
       <c r="T149" s="4"/>
@@ -26595,7 +26769,7 @@
       </c>
       <c r="R150" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S150" s="4"/>
       <c r="T150" s="4"/>
@@ -26665,7 +26839,7 @@
       </c>
       <c r="R151" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S151" s="4"/>
       <c r="T151" s="4"/>
@@ -26733,7 +26907,7 @@
       </c>
       <c r="R152" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S152" s="4"/>
       <c r="T152" s="4"/>
@@ -26801,7 +26975,7 @@
       </c>
       <c r="R153" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S153" s="4"/>
       <c r="T153" s="4"/>
@@ -26869,7 +27043,7 @@
       </c>
       <c r="R154" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S154" s="4"/>
       <c r="T154" s="4"/>
@@ -26937,7 +27111,7 @@
       </c>
       <c r="R155" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S155" s="4"/>
       <c r="T155" s="4"/>
@@ -26975,7 +27149,7 @@
       </c>
       <c r="I156" s="21">
         <f t="shared" ca="1" si="14"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J156" s="8">
         <v>0</v>
@@ -27007,7 +27181,7 @@
       </c>
       <c r="R156" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S156" s="4"/>
       <c r="T156" s="4"/>
@@ -27075,7 +27249,7 @@
       </c>
       <c r="R157" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S157" s="4"/>
       <c r="T157" s="4"/>
@@ -27143,7 +27317,7 @@
       </c>
       <c r="R158" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S158" s="4"/>
       <c r="T158" s="4"/>
@@ -27211,7 +27385,7 @@
       </c>
       <c r="R159" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S159" s="4"/>
       <c r="T159" s="4"/>
@@ -27279,7 +27453,7 @@
       </c>
       <c r="R160" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S160" s="4"/>
       <c r="T160" s="4"/>
@@ -27347,7 +27521,7 @@
       </c>
       <c r="R161" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S161" s="4"/>
       <c r="T161" s="4"/>
@@ -27415,7 +27589,7 @@
       </c>
       <c r="R162" s="4">
         <f ca="1">DATEDIF(TODAY(),O162,"m")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S162" s="4"/>
       <c r="T162" s="4"/>
@@ -27485,7 +27659,7 @@
       </c>
       <c r="R163" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S163" s="4"/>
       <c r="T163" s="4"/>
@@ -27553,7 +27727,7 @@
       </c>
       <c r="R164" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S164" s="4"/>
       <c r="T164" s="4"/>
@@ -27621,7 +27795,7 @@
       </c>
       <c r="R165" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S165" s="4"/>
       <c r="T165" s="4"/>
@@ -27691,7 +27865,7 @@
       </c>
       <c r="R166" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S166" s="4"/>
       <c r="T166" s="4"/>
@@ -27761,7 +27935,7 @@
       </c>
       <c r="R167" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S167" s="4"/>
       <c r="T167" s="4"/>
@@ -27829,7 +28003,7 @@
       </c>
       <c r="R168" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S168" s="4"/>
       <c r="T168" s="4"/>
@@ -27897,7 +28071,7 @@
       </c>
       <c r="R169" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S169" s="4"/>
       <c r="T169" s="4"/>
@@ -27933,7 +28107,7 @@
       </c>
       <c r="I170" s="21">
         <f t="shared" ca="1" si="14"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J170" s="8">
         <v>9000000</v>
@@ -27965,7 +28139,7 @@
       </c>
       <c r="R170" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S170" s="4"/>
       <c r="T170" s="4"/>
@@ -28033,7 +28207,7 @@
       </c>
       <c r="R171" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S171" s="4"/>
       <c r="T171" s="4"/>
@@ -28069,7 +28243,7 @@
       </c>
       <c r="I172" s="21">
         <f ca="1">DATEDIF(H172,TODAY(),"Y")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J172" s="8">
         <v>12000000</v>
@@ -28101,7 +28275,7 @@
       </c>
       <c r="R172" s="4">
         <f ca="1">DATEDIF(TODAY(),O172,"m")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S172" s="4"/>
       <c r="T172" s="4"/>
@@ -28171,7 +28345,7 @@
       </c>
       <c r="R173" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S173" s="4"/>
       <c r="T173" s="4"/>
@@ -28239,7 +28413,7 @@
       </c>
       <c r="R174" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S174" s="4"/>
       <c r="T174" s="4"/>
@@ -28309,7 +28483,7 @@
       </c>
       <c r="R175" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S175" s="4"/>
       <c r="T175" s="4"/>
@@ -28377,7 +28551,7 @@
       </c>
       <c r="R176" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S176" s="4"/>
       <c r="T176" s="4"/>
@@ -28445,7 +28619,7 @@
       </c>
       <c r="R177" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S177" s="4"/>
       <c r="T177" s="4"/>
@@ -28513,7 +28687,7 @@
       </c>
       <c r="R178" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S178" s="4"/>
       <c r="T178" s="4"/>
@@ -28583,7 +28757,7 @@
       </c>
       <c r="R179" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S179" s="4"/>
       <c r="T179" s="4"/>
@@ -28651,7 +28825,7 @@
       </c>
       <c r="R180" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S180" s="4"/>
       <c r="T180" s="4"/>
@@ -28721,7 +28895,7 @@
       </c>
       <c r="R181" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S181" s="4"/>
       <c r="T181" s="4"/>
@@ -28791,7 +28965,7 @@
       </c>
       <c r="R182" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S182" s="4"/>
       <c r="T182" s="4"/>
@@ -28861,7 +29035,7 @@
       </c>
       <c r="R183" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S183" s="4"/>
       <c r="T183" s="4"/>
@@ -28931,7 +29105,7 @@
       </c>
       <c r="R184" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S184" s="4"/>
       <c r="T184" s="4"/>
@@ -29001,7 +29175,7 @@
       </c>
       <c r="R185" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S185" s="4"/>
       <c r="T185" s="4"/>
@@ -29071,7 +29245,7 @@
       </c>
       <c r="R186" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S186" s="4"/>
       <c r="T186" s="4"/>
@@ -29141,7 +29315,7 @@
       </c>
       <c r="R187" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S187" s="4"/>
       <c r="T187" s="4"/>
@@ -29211,7 +29385,7 @@
       </c>
       <c r="R188" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S188" s="4"/>
       <c r="T188" s="4"/>
@@ -29281,7 +29455,7 @@
       </c>
       <c r="R189" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S189" s="4"/>
       <c r="T189" s="4"/>
@@ -29351,7 +29525,7 @@
       </c>
       <c r="R190" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S190" s="4"/>
       <c r="T190" s="4"/>
@@ -29421,7 +29595,7 @@
       </c>
       <c r="R191" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S191" s="4"/>
       <c r="T191" s="4"/>
@@ -29459,7 +29633,7 @@
       </c>
       <c r="I192" s="21">
         <f t="shared" ca="1" si="14"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J192" s="8">
         <v>0</v>
@@ -29491,7 +29665,7 @@
       </c>
       <c r="R192" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S192" s="4"/>
       <c r="T192" s="4"/>
@@ -29561,7 +29735,7 @@
       </c>
       <c r="R193" s="4">
         <f ca="1">DATEDIF(TODAY(),O193,"m")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S193" s="4"/>
       <c r="T193" s="4"/>
@@ -29631,7 +29805,7 @@
       </c>
       <c r="R194" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S194" s="4"/>
       <c r="T194" s="4"/>
@@ -29701,7 +29875,7 @@
       </c>
       <c r="R195" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S195" s="4"/>
       <c r="T195" s="4"/>
@@ -29771,7 +29945,7 @@
       </c>
       <c r="R196" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S196" s="4"/>
       <c r="T196" s="4"/>
@@ -29841,7 +30015,7 @@
       </c>
       <c r="R197" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S197" s="4"/>
       <c r="T197" s="4"/>
@@ -29911,7 +30085,7 @@
       </c>
       <c r="R198" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S198" s="4"/>
       <c r="T198" s="4"/>
@@ -29981,7 +30155,7 @@
       </c>
       <c r="R199" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S199" s="4"/>
       <c r="T199" s="4"/>
@@ -30053,7 +30227,7 @@
       </c>
       <c r="R200" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S200" s="4"/>
       <c r="T200" s="4"/>
@@ -30121,7 +30295,7 @@
       </c>
       <c r="R201" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S201" s="4"/>
       <c r="T201" s="4"/>
@@ -30189,7 +30363,7 @@
       </c>
       <c r="R202" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S202" s="4"/>
       <c r="T202" s="4"/>
@@ -30257,7 +30431,7 @@
       </c>
       <c r="R203" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S203" s="4"/>
       <c r="T203" s="4"/>
@@ -30325,7 +30499,7 @@
       </c>
       <c r="R204" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S204" s="4"/>
       <c r="T204" s="4"/>
@@ -30393,7 +30567,7 @@
       </c>
       <c r="R205" s="4">
         <f t="shared" ref="R205:R274" ca="1" si="21">DATEDIF(TODAY(),O205,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S205" s="4"/>
       <c r="T205" s="4"/>
@@ -30429,7 +30603,7 @@
       </c>
       <c r="I206" s="21">
         <f t="shared" ca="1" si="18"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J206" s="8">
         <v>0</v>
@@ -30461,7 +30635,7 @@
       </c>
       <c r="R206" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S206" s="4"/>
       <c r="T206" s="4"/>
@@ -30565,7 +30739,7 @@
       </c>
       <c r="I208" s="21">
         <f t="shared" ca="1" si="18"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J208" s="8">
         <v>0</v>
@@ -30597,7 +30771,7 @@
       </c>
       <c r="R208" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S208" s="4"/>
       <c r="T208" s="4"/>
@@ -30665,7 +30839,7 @@
       </c>
       <c r="R209" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S209" s="4"/>
       <c r="T209" s="4"/>
@@ -30733,7 +30907,7 @@
       </c>
       <c r="R210" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S210" s="4"/>
       <c r="T210" s="4"/>
@@ -30801,7 +30975,7 @@
       </c>
       <c r="R211" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S211" s="4"/>
       <c r="T211" s="4"/>
@@ -30869,7 +31043,7 @@
       </c>
       <c r="R212" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S212" s="4"/>
       <c r="T212" s="4"/>
@@ -30937,7 +31111,7 @@
       </c>
       <c r="R213" s="4">
         <f ca="1">DATEDIF(TODAY(),O213,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S213" s="4"/>
       <c r="T213" s="4"/>
@@ -31007,7 +31181,7 @@
       </c>
       <c r="R214" s="4">
         <f ca="1">DATEDIF(TODAY(),O214,"m")</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S214" s="4"/>
       <c r="T214" s="4"/>
@@ -31075,7 +31249,7 @@
       </c>
       <c r="R215" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S215" s="4"/>
       <c r="T215" s="4"/>
@@ -31145,7 +31319,7 @@
       </c>
       <c r="R216" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S216" s="4"/>
       <c r="T216" s="4"/>
@@ -31215,7 +31389,7 @@
       </c>
       <c r="R217" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S217" s="4"/>
       <c r="T217" s="4"/>
@@ -31283,7 +31457,7 @@
       </c>
       <c r="R218" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S218" s="4"/>
       <c r="T218" s="4"/>
@@ -31353,7 +31527,7 @@
       </c>
       <c r="R219" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S219" s="4"/>
       <c r="T219" s="4"/>
@@ -31421,7 +31595,7 @@
       </c>
       <c r="R220" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S220" s="4"/>
       <c r="T220" s="4"/>
@@ -31489,7 +31663,7 @@
       </c>
       <c r="R221" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S221" s="4"/>
       <c r="T221" s="4"/>
@@ -31557,7 +31731,7 @@
       </c>
       <c r="R222" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S222" s="4"/>
       <c r="T222" s="4"/>
@@ -31625,7 +31799,7 @@
       </c>
       <c r="R223" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S223" s="4"/>
       <c r="T223" s="4"/>
@@ -31693,7 +31867,7 @@
       </c>
       <c r="R224" s="4">
         <f ca="1">DATEDIF(TODAY(),O224,"m")</f>
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S224" s="4"/>
       <c r="T224" s="4"/>
@@ -31761,7 +31935,7 @@
       </c>
       <c r="R225" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S225" s="4"/>
       <c r="T225" s="4"/>
@@ -31829,7 +32003,7 @@
       </c>
       <c r="R226" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S226" s="4"/>
       <c r="T226" s="4"/>
@@ -31897,7 +32071,7 @@
       </c>
       <c r="R227" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S227" s="4"/>
       <c r="T227" s="4"/>
@@ -31965,7 +32139,7 @@
       </c>
       <c r="R228" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S228" s="4"/>
       <c r="T228" s="4"/>
@@ -32033,7 +32207,7 @@
       </c>
       <c r="R229" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S229" s="4"/>
       <c r="T229" s="4"/>
@@ -32101,7 +32275,7 @@
       </c>
       <c r="R230" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S230" s="4"/>
       <c r="T230" s="4"/>
@@ -32169,7 +32343,7 @@
       </c>
       <c r="R231" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S231" s="4"/>
       <c r="T231" s="4"/>
@@ -32237,7 +32411,7 @@
       </c>
       <c r="R232" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S232" s="4"/>
       <c r="T232" s="4"/>
@@ -32305,7 +32479,7 @@
       </c>
       <c r="R233" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S233" s="4"/>
       <c r="T233" s="4"/>
@@ -32373,7 +32547,7 @@
       </c>
       <c r="R234" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S234" s="4"/>
       <c r="T234" s="4"/>
@@ -32441,7 +32615,7 @@
       </c>
       <c r="R235" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S235" s="4"/>
       <c r="T235" s="4"/>
@@ -32509,7 +32683,7 @@
       </c>
       <c r="R236" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S236" s="4"/>
       <c r="T236" s="4"/>
@@ -32579,7 +32753,7 @@
       </c>
       <c r="R237" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S237" s="4"/>
       <c r="T237" s="4"/>
@@ -32647,7 +32821,7 @@
       </c>
       <c r="R238" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S238" s="4"/>
       <c r="T238" s="4"/>
@@ -32715,7 +32889,7 @@
       </c>
       <c r="R239" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S239" s="4"/>
       <c r="T239" s="4"/>
@@ -32785,7 +32959,7 @@
       </c>
       <c r="R240" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S240" s="4"/>
       <c r="T240" s="4"/>
@@ -32853,7 +33027,7 @@
       </c>
       <c r="R241" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="S241" s="4"/>
       <c r="T241" s="4"/>
@@ -32921,7 +33095,7 @@
       </c>
       <c r="R242" s="4">
         <f ca="1">DATEDIF(TODAY(),O242,"m")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S242" s="4"/>
       <c r="T242" s="4"/>
@@ -32991,7 +33165,7 @@
       </c>
       <c r="R243" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S243" s="4"/>
       <c r="T243" s="4"/>
@@ -33059,7 +33233,7 @@
       </c>
       <c r="R244" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S244" s="4"/>
       <c r="T244" s="4"/>
@@ -33127,7 +33301,7 @@
       </c>
       <c r="R245" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S245" s="4"/>
       <c r="T245" s="4"/>
@@ -33195,7 +33369,7 @@
       </c>
       <c r="R246" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S246" s="4"/>
       <c r="T246" s="4"/>
@@ -33263,7 +33437,7 @@
       </c>
       <c r="R247" s="4">
         <f ca="1">DATEDIF(TODAY(),O247,"m")</f>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S247" s="4"/>
       <c r="T247" s="4"/>
@@ -33331,7 +33505,7 @@
       </c>
       <c r="R248" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S248" s="4"/>
       <c r="T248" s="4"/>
@@ -33399,7 +33573,7 @@
       </c>
       <c r="R249" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S249" s="4"/>
       <c r="T249" s="4"/>
@@ -33467,7 +33641,7 @@
       </c>
       <c r="R250" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S250" s="4"/>
       <c r="T250" s="4"/>
@@ -33535,7 +33709,7 @@
       </c>
       <c r="R251" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S251" s="4"/>
       <c r="T251" s="4"/>
@@ -33605,7 +33779,7 @@
       </c>
       <c r="R252" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S252" s="4"/>
       <c r="T252" s="4"/>
@@ -33673,7 +33847,7 @@
       </c>
       <c r="R253" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S253" s="4"/>
       <c r="T253" s="4"/>
@@ -33741,7 +33915,7 @@
       </c>
       <c r="R254" s="4">
         <f ca="1">DATEDIF(TODAY(),O254,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S254" s="4"/>
       <c r="T254" s="4"/>
@@ -33809,7 +33983,7 @@
       </c>
       <c r="R255" s="4">
         <f ca="1">DATEDIF(TODAY(),O255,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S255" s="4"/>
       <c r="T255" s="4"/>
@@ -33877,7 +34051,7 @@
       </c>
       <c r="R256" s="4">
         <f ca="1">DATEDIF(TODAY(),O256,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S256" s="4"/>
       <c r="T256" s="4"/>
@@ -33945,7 +34119,7 @@
       </c>
       <c r="R257" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S257" s="4"/>
       <c r="T257" s="4"/>
@@ -34013,7 +34187,7 @@
       </c>
       <c r="R258" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S258" s="4"/>
       <c r="T258" s="4"/>
@@ -34081,7 +34255,7 @@
       </c>
       <c r="R259" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S259" s="4"/>
       <c r="T259" s="4"/>
@@ -34149,7 +34323,7 @@
       </c>
       <c r="R260" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S260" s="4"/>
       <c r="T260" s="4"/>
@@ -34217,7 +34391,7 @@
       </c>
       <c r="R261" s="4">
         <f ca="1">DATEDIF(TODAY(),O261,"m")</f>
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S261" s="4"/>
       <c r="T261" s="4"/>
@@ -34285,7 +34459,7 @@
       </c>
       <c r="R262" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S262" s="4"/>
       <c r="T262" s="4"/>
@@ -34353,7 +34527,7 @@
       </c>
       <c r="R263" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S263" s="4"/>
       <c r="T263" s="4"/>
@@ -34421,7 +34595,7 @@
       </c>
       <c r="R264" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S264" s="4"/>
       <c r="T264" s="4"/>
@@ -34457,7 +34631,7 @@
       </c>
       <c r="I265" s="21">
         <f t="shared" ca="1" si="18"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J265" s="8">
         <v>0</v>
@@ -34489,7 +34663,7 @@
       </c>
       <c r="R265" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S265" s="4"/>
       <c r="T265" s="4"/>
@@ -34557,7 +34731,7 @@
       </c>
       <c r="R266" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S266" s="4"/>
       <c r="T266" s="4"/>
@@ -34625,7 +34799,7 @@
       </c>
       <c r="R267" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S267" s="4"/>
       <c r="T267" s="4"/>
@@ -34695,7 +34869,7 @@
       </c>
       <c r="R268" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S268" s="4"/>
       <c r="T268" s="4"/>
@@ -34763,7 +34937,7 @@
       </c>
       <c r="R269" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S269" s="4"/>
       <c r="T269" s="4"/>
@@ -34831,7 +35005,7 @@
       </c>
       <c r="R270" s="4">
         <f ca="1">DATEDIF(TODAY(),O270,"m")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S270" s="4"/>
       <c r="T270" s="4"/>
@@ -34899,7 +35073,7 @@
       </c>
       <c r="R271" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S271" s="4"/>
       <c r="T271" s="4"/>
@@ -34967,7 +35141,7 @@
       </c>
       <c r="R272" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S272" s="4"/>
       <c r="T272" s="4"/>
@@ -35035,7 +35209,7 @@
       </c>
       <c r="R273" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S273" s="4"/>
       <c r="T273" s="4"/>
@@ -35103,7 +35277,7 @@
       </c>
       <c r="R274" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S274" s="4"/>
       <c r="T274" s="4"/>
@@ -35173,7 +35347,7 @@
       </c>
       <c r="R275" s="4">
         <f t="shared" ref="R275:R342" ca="1" si="25">DATEDIF(TODAY(),O275,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S275" s="4"/>
       <c r="T275" s="4"/>
@@ -35241,7 +35415,7 @@
       </c>
       <c r="R276" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S276" s="4"/>
       <c r="T276" s="4"/>
@@ -35309,7 +35483,7 @@
       </c>
       <c r="R277" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S277" s="4"/>
       <c r="T277" s="4"/>
@@ -35377,7 +35551,7 @@
       </c>
       <c r="R278" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S278" s="4"/>
       <c r="T278" s="4"/>
@@ -35447,7 +35621,7 @@
       </c>
       <c r="R279" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S279" s="4"/>
       <c r="T279" s="4"/>
@@ -35483,7 +35657,7 @@
       </c>
       <c r="I280" s="21">
         <f t="shared" ca="1" si="22"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J280" s="8">
         <v>8000000</v>
@@ -35515,7 +35689,7 @@
       </c>
       <c r="R280" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S280" s="4"/>
       <c r="T280" s="4"/>
@@ -35583,7 +35757,7 @@
       </c>
       <c r="R281" s="4">
         <f t="shared" ref="R281" ca="1" si="28">DATEDIF(TODAY(),O281,"m")</f>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S281" s="4"/>
       <c r="T281" s="4"/>
@@ -35651,7 +35825,7 @@
       </c>
       <c r="R282" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S282" s="4"/>
       <c r="T282" s="4"/>
@@ -35719,7 +35893,7 @@
       </c>
       <c r="R283" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S283" s="4"/>
       <c r="T283" s="4"/>
@@ -35787,7 +35961,7 @@
       </c>
       <c r="R284" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S284" s="4"/>
       <c r="T284" s="4"/>
@@ -35855,7 +36029,7 @@
       </c>
       <c r="R285" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S285" s="4"/>
       <c r="T285" s="4"/>
@@ -35923,7 +36097,7 @@
       </c>
       <c r="R286" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S286" s="4"/>
       <c r="T286" s="4"/>
@@ -35991,7 +36165,7 @@
       </c>
       <c r="R287" s="4">
         <f ca="1">DATEDIF(TODAY(),O287,"m")</f>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S287" s="4"/>
       <c r="T287" s="4"/>
@@ -36027,7 +36201,7 @@
       </c>
       <c r="I288" s="21">
         <f t="shared" ca="1" si="22"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J288" s="8">
         <v>0</v>
@@ -36059,7 +36233,7 @@
       </c>
       <c r="R288" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S288" s="4"/>
       <c r="T288" s="4"/>
@@ -36129,7 +36303,7 @@
       </c>
       <c r="R289" s="4">
         <f ca="1">DATEDIF(TODAY(),O289,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S289" s="4"/>
       <c r="T289" s="4"/>
@@ -36197,7 +36371,7 @@
       </c>
       <c r="R290" s="4">
         <f ca="1">DATEDIF(TODAY(),O290,"m")</f>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S290" s="4"/>
       <c r="T290" s="4"/>
@@ -36265,7 +36439,7 @@
       </c>
       <c r="R291" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S291" s="4"/>
       <c r="T291" s="4"/>
@@ -36333,7 +36507,7 @@
       </c>
       <c r="R292" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S292" s="4"/>
       <c r="T292" s="4"/>
@@ -36401,7 +36575,7 @@
       </c>
       <c r="R293" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S293" s="4"/>
       <c r="T293" s="4"/>
@@ -36469,7 +36643,7 @@
       </c>
       <c r="R294" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S294" s="4"/>
       <c r="T294" s="4"/>
@@ -36537,7 +36711,7 @@
       </c>
       <c r="R295" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S295" s="4"/>
       <c r="T295" s="4"/>
@@ -36605,7 +36779,7 @@
       </c>
       <c r="R296" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S296" s="4"/>
       <c r="T296" s="4"/>
@@ -36743,7 +36917,7 @@
       </c>
       <c r="R298" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S298" s="4"/>
       <c r="T298" s="4"/>
@@ -36811,7 +36985,7 @@
       </c>
       <c r="R299" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S299" s="4"/>
       <c r="T299" s="4"/>
@@ -36879,7 +37053,7 @@
       </c>
       <c r="R300" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S300" s="4"/>
       <c r="T300" s="4"/>
@@ -36947,7 +37121,7 @@
       </c>
       <c r="R301" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S301" s="4"/>
       <c r="T301" s="4"/>
@@ -37015,7 +37189,7 @@
       </c>
       <c r="R302" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S302" s="4"/>
       <c r="T302" s="4"/>
@@ -37085,7 +37259,7 @@
       </c>
       <c r="R303" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S303" s="4"/>
       <c r="T303" s="4"/>
@@ -37153,7 +37327,7 @@
       </c>
       <c r="R304" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S304" s="4"/>
       <c r="T304" s="4"/>
@@ -37221,7 +37395,7 @@
       </c>
       <c r="R305" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S305" s="4"/>
       <c r="T305" s="4"/>
@@ -37289,7 +37463,7 @@
       </c>
       <c r="R306" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S306" s="4"/>
       <c r="T306" s="4"/>
@@ -37357,7 +37531,7 @@
       </c>
       <c r="R307" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S307" s="4"/>
       <c r="T307" s="4"/>
@@ -37425,7 +37599,7 @@
       </c>
       <c r="R308" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S308" s="4"/>
       <c r="T308" s="4"/>
@@ -37493,7 +37667,7 @@
       </c>
       <c r="R309" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S309" s="4"/>
       <c r="T309" s="4"/>
@@ -37561,7 +37735,7 @@
       </c>
       <c r="R310" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S310" s="4"/>
       <c r="T310" s="4"/>
@@ -37629,7 +37803,7 @@
       </c>
       <c r="R311" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S311" s="4"/>
       <c r="T311" s="4"/>
@@ -37697,7 +37871,7 @@
       </c>
       <c r="R312" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S312" s="4"/>
       <c r="T312" s="4"/>
@@ -37765,7 +37939,7 @@
       </c>
       <c r="R313" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S313" s="4"/>
       <c r="T313" s="4"/>
@@ -37833,7 +38007,7 @@
       </c>
       <c r="R314" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S314" s="4"/>
       <c r="T314" s="4"/>
@@ -37901,7 +38075,7 @@
       </c>
       <c r="R315" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S315" s="4"/>
       <c r="T315" s="4"/>
@@ -37969,7 +38143,7 @@
       </c>
       <c r="R316" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S316" s="4"/>
       <c r="T316" s="4"/>
@@ -38037,7 +38211,7 @@
       </c>
       <c r="R317" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S317" s="4"/>
       <c r="T317" s="4"/>
@@ -38105,7 +38279,7 @@
       </c>
       <c r="R318" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S318" s="4"/>
       <c r="T318" s="4"/>
@@ -38173,7 +38347,7 @@
       </c>
       <c r="R319" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S319" s="4"/>
       <c r="T319" s="4"/>
@@ -38241,7 +38415,7 @@
       </c>
       <c r="R320" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S320" s="4"/>
       <c r="T320" s="4"/>
@@ -38309,7 +38483,7 @@
       </c>
       <c r="R321" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S321" s="4"/>
       <c r="T321" s="4"/>
@@ -38377,7 +38551,7 @@
       </c>
       <c r="R322" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S322" s="4"/>
       <c r="T322" s="4"/>
@@ -38445,7 +38619,7 @@
       </c>
       <c r="R323" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S323" s="4"/>
       <c r="T323" s="4"/>
@@ -38513,7 +38687,7 @@
       </c>
       <c r="R324" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S324" s="4"/>
       <c r="T324" s="4"/>
@@ -38581,7 +38755,7 @@
       </c>
       <c r="R325" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S325" s="4"/>
       <c r="T325" s="4"/>
@@ -38651,7 +38825,7 @@
       </c>
       <c r="R326" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S326" s="4"/>
       <c r="T326" s="4"/>
@@ -38719,7 +38893,7 @@
       </c>
       <c r="R327" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S327" s="4"/>
       <c r="T327" s="4"/>
@@ -38787,7 +38961,7 @@
       </c>
       <c r="R328" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S328" s="4"/>
       <c r="T328" s="4"/>
@@ -38855,7 +39029,7 @@
       </c>
       <c r="R329" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S329" s="4"/>
       <c r="T329" s="4"/>
@@ -38923,7 +39097,7 @@
       </c>
       <c r="R330" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S330" s="4"/>
       <c r="T330" s="4"/>
@@ -38991,7 +39165,7 @@
       </c>
       <c r="R331" s="4">
         <f ca="1">DATEDIF(TODAY(),O331,"m")</f>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S331" s="4"/>
       <c r="T331" s="4"/>
@@ -39059,7 +39233,7 @@
       </c>
       <c r="R332" s="4">
         <f ca="1">DATEDIF(TODAY(),O332,"m")</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S332" s="4"/>
       <c r="T332" s="4"/>
@@ -39127,7 +39301,7 @@
       </c>
       <c r="R333" s="4">
         <f ca="1">DATEDIF(TODAY(),O333,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S333" s="4"/>
       <c r="T333" s="4"/>
@@ -39195,7 +39369,7 @@
       </c>
       <c r="R334" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S334" s="4"/>
       <c r="T334" s="4"/>
@@ -39265,7 +39439,7 @@
       </c>
       <c r="R335" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S335" s="4"/>
       <c r="T335" s="4"/>
@@ -39333,7 +39507,7 @@
       </c>
       <c r="R336" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S336" s="4"/>
       <c r="T336" s="4"/>
@@ -39401,7 +39575,7 @@
       </c>
       <c r="R337" s="4">
         <f ca="1">DATEDIF(TODAY(),O337,"m")</f>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S337" s="4"/>
       <c r="T337" s="4"/>
@@ -39469,7 +39643,7 @@
       </c>
       <c r="R338" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S338" s="4"/>
       <c r="T338" s="4"/>
@@ -39537,7 +39711,7 @@
       </c>
       <c r="R339" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S339" s="4"/>
       <c r="T339" s="4"/>
@@ -39603,7 +39777,7 @@
       </c>
       <c r="R340" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S340" s="4"/>
       <c r="T340" s="4"/>
@@ -39669,7 +39843,7 @@
       </c>
       <c r="R341" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S341" s="4"/>
       <c r="T341" s="4"/>
@@ -39735,7 +39909,7 @@
       </c>
       <c r="R342" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S342" s="4"/>
       <c r="T342" s="4"/>
@@ -39771,7 +39945,7 @@
       </c>
       <c r="I343" s="21">
         <f t="shared" ref="I343:I363" ca="1" si="29">DATEDIF(H343,TODAY(),"Y")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J343" s="8"/>
       <c r="K343" s="8">
@@ -39801,7 +39975,7 @@
       </c>
       <c r="R343" s="4">
         <f t="shared" ref="R343:R363" ca="1" si="32">DATEDIF(TODAY(),O343,"m")</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S343" s="4"/>
       <c r="T343" s="4"/>
@@ -39867,7 +40041,7 @@
       </c>
       <c r="R344" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S344" s="4"/>
       <c r="T344" s="4"/>
@@ -39933,7 +40107,7 @@
       </c>
       <c r="R345" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S345" s="4"/>
       <c r="T345" s="4"/>
@@ -39999,7 +40173,7 @@
       </c>
       <c r="R346" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S346" s="4"/>
       <c r="T346" s="4"/>
@@ -40065,7 +40239,7 @@
       </c>
       <c r="R347" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S347" s="4"/>
       <c r="T347" s="4"/>
@@ -40131,7 +40305,7 @@
       </c>
       <c r="R348" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S348" s="4"/>
       <c r="T348" s="4"/>
@@ -40197,7 +40371,7 @@
       </c>
       <c r="R349" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S349" s="4"/>
       <c r="T349" s="4"/>
@@ -40267,7 +40441,7 @@
       </c>
       <c r="R350" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S350" s="4"/>
       <c r="T350" s="4"/>
@@ -40333,7 +40507,7 @@
       </c>
       <c r="R351" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S351" s="4"/>
       <c r="T351" s="4"/>
@@ -40399,7 +40573,7 @@
       </c>
       <c r="R352" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S352" s="4"/>
       <c r="T352" s="4"/>
@@ -40465,7 +40639,7 @@
       </c>
       <c r="R353" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S353" s="4"/>
       <c r="T353" s="4"/>
@@ -40501,7 +40675,7 @@
       </c>
       <c r="I354" s="21">
         <f t="shared" ca="1" si="29"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J354" s="8"/>
       <c r="K354" s="8">
@@ -40531,7 +40705,7 @@
       </c>
       <c r="R354" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S354" s="4"/>
       <c r="T354" s="4"/>
@@ -40597,7 +40771,7 @@
       </c>
       <c r="R355" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S355" s="4"/>
       <c r="T355" s="4"/>
@@ -40663,7 +40837,7 @@
       </c>
       <c r="R356" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S356" s="4"/>
       <c r="T356" s="4"/>
@@ -40729,7 +40903,7 @@
       </c>
       <c r="R357" s="4">
         <f ca="1">DATEDIF(TODAY(),O357,"m")</f>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S357" s="4"/>
       <c r="T357" s="4"/>
@@ -40795,7 +40969,7 @@
       </c>
       <c r="R358" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S358" s="4"/>
       <c r="T358" s="4"/>
@@ -40861,7 +41035,7 @@
       </c>
       <c r="R359" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S359" s="4"/>
       <c r="T359" s="4"/>
@@ -40929,7 +41103,7 @@
       </c>
       <c r="R360" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S360" s="4"/>
       <c r="T360" s="4"/>
@@ -40995,7 +41169,7 @@
       </c>
       <c r="R361" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S361" s="4"/>
       <c r="T361" s="4"/>
@@ -41061,7 +41235,7 @@
       </c>
       <c r="R362" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S362" s="4"/>
       <c r="T362" s="4"/>
@@ -41127,7 +41301,7 @@
       </c>
       <c r="R363" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S363" s="4"/>
       <c r="T363" s="4"/>
@@ -41195,7 +41369,7 @@
       </c>
       <c r="R364" s="4">
         <f ca="1">DATEDIF(TODAY(),O364,"m")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S364" s="4"/>
       <c r="T364" s="4"/>
@@ -41233,7 +41407,7 @@
       </c>
       <c r="I365" s="21">
         <f t="shared" ref="I365:I386" ca="1" si="33">DATEDIF(H365,TODAY(),"Y")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J365" s="8">
         <v>10000</v>
@@ -41265,7 +41439,7 @@
       </c>
       <c r="R365" s="4">
         <f t="shared" ref="R365:R386" ca="1" si="36">DATEDIF(TODAY(),O365,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S365" s="4"/>
       <c r="T365" s="4"/>
@@ -41333,7 +41507,7 @@
       </c>
       <c r="R366" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S366" s="4"/>
       <c r="T366" s="4"/>
@@ -41401,7 +41575,7 @@
       </c>
       <c r="R367" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S367" s="4"/>
       <c r="T367" s="4"/>
@@ -41469,7 +41643,7 @@
       </c>
       <c r="R368" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S368" s="4"/>
       <c r="T368" s="4"/>
@@ -41537,7 +41711,7 @@
       </c>
       <c r="R369" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S369" s="4"/>
       <c r="T369" s="4"/>
@@ -41573,7 +41747,7 @@
       </c>
       <c r="I370" s="21">
         <f t="shared" ca="1" si="33"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J370" s="8">
         <v>0</v>
@@ -41605,7 +41779,7 @@
       </c>
       <c r="R370" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S370" s="4"/>
       <c r="T370" s="4"/>
@@ -41673,7 +41847,7 @@
       </c>
       <c r="R371" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S371" s="4"/>
       <c r="T371" s="4"/>
@@ -41741,7 +41915,7 @@
       </c>
       <c r="R372" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S372" s="4"/>
       <c r="T372" s="4"/>
@@ -41809,7 +41983,7 @@
       </c>
       <c r="R373" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S373" s="4"/>
       <c r="T373" s="4"/>
@@ -41879,7 +42053,7 @@
       </c>
       <c r="R374" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S374" s="4"/>
       <c r="T374" s="4"/>
@@ -41947,7 +42121,7 @@
       </c>
       <c r="R375" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S375" s="4"/>
       <c r="T375" s="4"/>
@@ -42015,7 +42189,7 @@
       </c>
       <c r="R376" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S376" s="4"/>
       <c r="T376" s="4"/>
@@ -42083,7 +42257,7 @@
       </c>
       <c r="R377" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S377" s="4"/>
       <c r="T377" s="4"/>
@@ -42151,7 +42325,7 @@
       </c>
       <c r="R378" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S378" s="4"/>
       <c r="T378" s="4"/>
@@ -42219,7 +42393,7 @@
       </c>
       <c r="R379" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S379" s="4"/>
       <c r="T379" s="4"/>
@@ -42279,7 +42453,7 @@
       </c>
       <c r="P380" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q380" s="4">
         <f t="shared" ca="1" si="35"/>
@@ -42287,7 +42461,7 @@
       </c>
       <c r="R380" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S380" s="4"/>
       <c r="T380" s="4"/>
@@ -42355,7 +42529,7 @@
       </c>
       <c r="R381" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S381" s="4"/>
       <c r="T381" s="4"/>
@@ -42425,7 +42599,7 @@
       </c>
       <c r="R382" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S382" s="4"/>
       <c r="T382" s="4"/>
@@ -42493,7 +42667,7 @@
       </c>
       <c r="R383" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S383" s="4"/>
       <c r="T383" s="4"/>
@@ -42561,7 +42735,7 @@
       </c>
       <c r="R384" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S384" s="4"/>
       <c r="T384" s="4"/>
@@ -42629,7 +42803,7 @@
       </c>
       <c r="R385" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S385" s="4"/>
       <c r="T385" s="4"/>
@@ -42697,7 +42871,7 @@
       </c>
       <c r="R386" s="4">
         <f t="shared" ca="1" si="36"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S386" s="4"/>
       <c r="T386" s="4"/>
@@ -42767,7 +42941,7 @@
       </c>
       <c r="R387" s="4">
         <f ca="1">DATEDIF(TODAY(),O387,"m")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S387" s="4"/>
       <c r="T387" s="4"/>
@@ -42835,7 +43009,7 @@
       </c>
       <c r="R388" s="4">
         <f t="shared" ref="R388:R409" ca="1" si="40">DATEDIF(TODAY(),O388,"m")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S388" s="4"/>
       <c r="T388" s="4"/>
@@ -42905,7 +43079,7 @@
       </c>
       <c r="R389" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S389" s="4"/>
       <c r="T389" s="4"/>
@@ -42973,7 +43147,7 @@
       </c>
       <c r="R390" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S390" s="4"/>
       <c r="T390" s="4"/>
@@ -43041,7 +43215,7 @@
       </c>
       <c r="R391" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S391" s="4"/>
       <c r="T391" s="4"/>
@@ -43109,7 +43283,7 @@
       </c>
       <c r="R392" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S392" s="4"/>
       <c r="T392" s="4"/>
@@ -43177,7 +43351,7 @@
       </c>
       <c r="R393" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S393" s="4"/>
       <c r="T393" s="4"/>
@@ -43243,7 +43417,7 @@
       </c>
       <c r="R394" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S394" s="4"/>
       <c r="T394" s="4"/>
@@ -43311,7 +43485,7 @@
       </c>
       <c r="R395" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S395" s="4"/>
       <c r="T395" s="4"/>
@@ -43379,7 +43553,7 @@
       </c>
       <c r="R396" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S396" s="4"/>
       <c r="T396" s="4"/>
@@ -43447,7 +43621,7 @@
       </c>
       <c r="R397" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S397" s="4"/>
       <c r="T397" s="4"/>
@@ -43515,7 +43689,7 @@
       </c>
       <c r="R398" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S398" s="4"/>
       <c r="T398" s="4"/>
@@ -43583,7 +43757,7 @@
       </c>
       <c r="R399" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S399" s="4"/>
       <c r="T399" s="4"/>
@@ -43653,7 +43827,7 @@
       </c>
       <c r="R400" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S400" s="4"/>
       <c r="T400" s="4"/>
@@ -43717,7 +43891,7 @@
       </c>
       <c r="R401" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S401" s="4"/>
       <c r="T401" s="4"/>
@@ -43785,7 +43959,7 @@
       </c>
       <c r="R402" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S402" s="4"/>
       <c r="T402" s="4"/>
@@ -43849,7 +44023,7 @@
       </c>
       <c r="R403" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S403" s="4"/>
       <c r="T403" s="4"/>
@@ -43917,7 +44091,7 @@
       </c>
       <c r="R404" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S404" s="4"/>
       <c r="T404" s="4"/>
@@ -43987,7 +44161,7 @@
       </c>
       <c r="R405" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S405" s="4"/>
       <c r="T405" s="4"/>
@@ -44055,7 +44229,7 @@
       </c>
       <c r="R406" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S406" s="4"/>
       <c r="T406" s="4"/>
@@ -44123,7 +44297,7 @@
       </c>
       <c r="R407" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S407" s="4"/>
       <c r="T407" s="4"/>
@@ -44191,7 +44365,7 @@
       </c>
       <c r="R408" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S408" s="4"/>
       <c r="T408" s="4"/>
@@ -44259,7 +44433,7 @@
       </c>
       <c r="R409" s="4">
         <f t="shared" ca="1" si="40"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S409" s="4"/>
       <c r="T409" s="4"/>
@@ -44327,7 +44501,7 @@
       </c>
       <c r="R410" s="4">
         <f ca="1">DATEDIF(TODAY(),O410,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S410" s="4"/>
       <c r="T410" s="4"/>
@@ -44395,7 +44569,7 @@
       </c>
       <c r="R411" s="4">
         <f t="shared" ref="R411:R432" ca="1" si="44">DATEDIF(TODAY(),O411,"m")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S411" s="4"/>
       <c r="T411" s="4"/>
@@ -44463,7 +44637,7 @@
       </c>
       <c r="R412" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S412" s="4"/>
       <c r="T412" s="4"/>
@@ -44531,7 +44705,7 @@
       </c>
       <c r="R413" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S413" s="4"/>
       <c r="T413" s="4"/>
@@ -44599,7 +44773,7 @@
       </c>
       <c r="R414" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S414" s="4"/>
       <c r="T414" s="4"/>
@@ -44637,7 +44811,7 @@
       </c>
       <c r="I415" s="21">
         <f t="shared" ca="1" si="41"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J415" s="8">
         <v>13000000</v>
@@ -44669,7 +44843,7 @@
       </c>
       <c r="R415" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S415" s="4"/>
       <c r="T415" s="4"/>
@@ -44739,7 +44913,7 @@
       </c>
       <c r="R416" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S416" s="4"/>
       <c r="T416" s="4"/>
@@ -44807,7 +44981,7 @@
       </c>
       <c r="R417" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S417" s="4"/>
       <c r="T417" s="4"/>
@@ -44875,7 +45049,7 @@
       </c>
       <c r="R418" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S418" s="4"/>
       <c r="T418" s="4"/>
@@ -44943,7 +45117,7 @@
       </c>
       <c r="R419" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S419" s="4"/>
       <c r="T419" s="4"/>
@@ -45011,7 +45185,7 @@
       </c>
       <c r="R420" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S420" s="4"/>
       <c r="T420" s="4"/>
@@ -45079,7 +45253,7 @@
       </c>
       <c r="R421" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S421" s="4"/>
       <c r="T421" s="4"/>
@@ -45147,7 +45321,7 @@
       </c>
       <c r="R422" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S422" s="4"/>
       <c r="T422" s="4"/>
@@ -45215,7 +45389,7 @@
       </c>
       <c r="R423" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S423" s="4"/>
       <c r="T423" s="4"/>
@@ -45251,7 +45425,7 @@
       </c>
       <c r="I424" s="21">
         <f t="shared" ca="1" si="41"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J424" s="8">
         <v>6000000</v>
@@ -45283,7 +45457,7 @@
       </c>
       <c r="R424" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S424" s="4"/>
       <c r="T424" s="4"/>
@@ -45351,7 +45525,7 @@
       </c>
       <c r="R425" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S425" s="4"/>
       <c r="T425" s="4"/>
@@ -45419,7 +45593,7 @@
       </c>
       <c r="R426" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S426" s="4"/>
       <c r="T426" s="4"/>
@@ -45487,7 +45661,7 @@
       </c>
       <c r="R427" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S427" s="4"/>
       <c r="T427" s="4"/>
@@ -45555,7 +45729,7 @@
       </c>
       <c r="R428" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S428" s="4"/>
       <c r="T428" s="4"/>
@@ -45623,7 +45797,7 @@
       </c>
       <c r="R429" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S429" s="4"/>
       <c r="T429" s="4"/>
@@ -45691,7 +45865,7 @@
       </c>
       <c r="R430" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S430" s="4"/>
       <c r="T430" s="4"/>
@@ -45759,7 +45933,7 @@
       </c>
       <c r="R431" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S431" s="4"/>
       <c r="T431" s="4"/>
@@ -45827,7 +46001,7 @@
       </c>
       <c r="R432" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S432" s="4"/>
       <c r="T432" s="4"/>
@@ -45895,7 +46069,7 @@
       </c>
       <c r="R433" s="4">
         <f t="shared" ref="R433:R434" ca="1" si="48">DATEDIF(TODAY(),O433,"m")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S433" s="4"/>
       <c r="T433" s="4"/>
@@ -45963,7 +46137,7 @@
       </c>
       <c r="R434" s="4">
         <f t="shared" ca="1" si="48"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S434" s="4"/>
       <c r="T434" s="4"/>
@@ -45996,7 +46170,7 @@
       </c>
       <c r="I435" s="26">
         <f ca="1">SUBTOTAL(101,Table2[AGE])</f>
-        <v>24.856812933025402</v>
+        <v>24.912240184757504</v>
       </c>
       <c r="J435" s="30">
         <f>SUBTOTAL(109,Table2[Signed for])</f>
@@ -46005,7 +46179,7 @@
       <c r="K435" s="30">
         <f>SUBTOTAL(109,Table2[Market 
 Value])</f>
-        <v>8932895000</v>
+        <v>8947895000</v>
       </c>
       <c r="L435" s="30">
         <f>SUBTOTAL(109,Table2[Salary/
@@ -46294,7 +46468,7 @@
       </c>
       <c r="K5" s="4">
         <f ca="1">DATEDIF(Table3[[#This Row],[DOB]],TODAY(),"Y")</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L5" s="4">
         <f>DATEDIF(Table3[[#This Row],[DOB]],Table3[[#This Row],[Transfer Date]],"Y")</f>
@@ -48984,7 +49158,7 @@
       </c>
       <c r="K61" s="4">
         <f ca="1">DATEDIF(Table3[[#This Row],[DOB]],TODAY(),"Y")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L61" s="4" t="e">
         <f>DATEDIF(Table3[[#This Row],[DOB]],Table3[[#This Row],[Transfer Date]],"Y")</f>
@@ -49338,7 +49512,7 @@
       <c r="J70" s="4"/>
       <c r="K70" s="4">
         <f ca="1">SUBTOTAL(101,Table3[Age])</f>
-        <v>31.279411764705884</v>
+        <v>31.308823529411764</v>
       </c>
       <c r="L70" s="4" t="e">
         <f>SUBTOTAL(101,Table3[Age at Transfer])</f>
